--- a/output/huggingface_models_2026-07-20.xlsx
+++ b/output/huggingface_models_2026-07-20.xlsx
@@ -11654,33 +11654,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>datumo/E-star-12B-base</t>
+          <t>LinerAI/Qwen3-Embedding-0.6B-academic</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>E-star-12B-base</t>
+          <t>Qwen3-Embedding-0.6B-academic</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>데이터모</t>
+          <t>라이너</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datumo/E-star-12B-base</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>https://huggingface.co/LinerAI/Qwen3-Embedding-0.6B-academic</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2205.13147</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>금융·법률 RAG 파이프라인 품질평가에 특화, 프런티어 모델 대비 저비용 자동평가 대안으로 적합</t>
+          <t>학술 검색 전용 파인튜닝으로 LitSearch·QASA 등에서 원본 대비 성능 향상, 학술 문헌 검색에 적합</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>법률·전문서비스</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11690,32 +11694,34 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
-        <v>46105</v>
+        <v>45989</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>46164</v>
+        <v>45989</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>11766034176</v>
-      </c>
-      <c r="N125" s="3" t="inlineStr"/>
+        <v>595776512</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>4096</v>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>FP32</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gemma3ForCausalLM</t>
+          <t>Qwen3ForCausalLM</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -11725,7 +11731,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-it</t>
+          <t>Qwen/Qwen3-Embedding-0.6B</t>
         </is>
       </c>
       <c r="S125" t="inlineStr"/>
@@ -11733,38 +11739,42 @@
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>SciFact=84.82;TRECCOVID=2.27;NFCorpus=17.39;SCIDOCS=23.23;LitSearch=69.44;QASA=35.70</t>
+        </is>
+      </c>
       <c r="Y125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>datumo/CAC-CoT</t>
+          <t>LinerAI/embeddinggemma-300m-academic</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CAC-CoT</t>
+          <t>embeddinggemma-300m-academic</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>데이터모</t>
+          <t>라이너</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datumo/CAC-CoT</t>
+          <t>https://huggingface.co/LinerAI/embeddinggemma-300m-academic</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.18743</t>
+          <t>https://arxiv.org/abs/2205.13147</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>연결어 기반 압축 CoT로 해석 가능한 추론을 저지연으로 제공해 수학·논리 튜터링과 설명 가능한 QA에 적합</t>
+          <t>학술 검색 전용 파인튜닝된 경량 임베딩 모델로, LitSearch·QASA에서 원본 대비 향상된 학술 문헌 검색에 적합</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11779,32 +11789,34 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
-        <v>45793</v>
+        <v>45989</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>45915</v>
+        <v>45989</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>7070619136</v>
-      </c>
-      <c r="N126" s="3" t="inlineStr"/>
+        <v>307581696</v>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>2048</v>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>FP32</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Qwen2Model</t>
+          <t>Gemma3TextModel</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -11814,7 +11826,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>Qwen/Qwen2.5-7B-Instruct</t>
+          <t>google/gemma-3-300m</t>
         </is>
       </c>
       <c r="S126" t="inlineStr"/>
@@ -11822,18 +11834,22 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>SciFact=88.63;TRECCOVID=1.86;NFCorpus=17.35;SCIDOCS=18.79;LitSearch=62.50;QASA=36.90</t>
+        </is>
+      </c>
       <c r="Y126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LinerAI/Qwen3-Embedding-0.6B-academic</t>
+          <t>LinerAI/snowflake-arctic-embed-l-v2.0-academic</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Qwen3-Embedding-0.6B-academic</t>
+          <t>snowflake-arctic-embed-l-v2.0-academic</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -11843,7 +11859,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://huggingface.co/LinerAI/Qwen3-Embedding-0.6B-academic</t>
+          <t>https://huggingface.co/LinerAI/snowflake-arctic-embed-l-v2.0-academic</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11853,7 +11869,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>학술 검색 전용 파인튜닝으로 LitSearch·QASA 등에서 원본 대비 성능 향상, 학술 문헌 검색에 적합</t>
+          <t>학술 검색 전용 파인튜닝으로 LitSearch·QASA 등에서 원본 대비 성능이 향상된 학술 문헌 검색용 임베딩</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -11868,7 +11884,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -11883,7 +11899,7 @@
         <v>45989</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>595776512</v>
+        <v>567754752</v>
       </c>
       <c r="N127" s="3" t="n">
         <v>4096</v>
@@ -11895,7 +11911,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Qwen3ForCausalLM</t>
+          <t>XLMRobertaModel</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -11905,7 +11921,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-Embedding-0.6B</t>
+          <t>Snowflake/snowflake-arctic-embed-l-v2.0</t>
         </is>
       </c>
       <c r="S127" t="inlineStr"/>
@@ -11915,7 +11931,7 @@
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
-          <t>SciFact=84.82;TRECCOVID=2.27;NFCorpus=17.39;SCIDOCS=23.23;LitSearch=69.44;QASA=35.70</t>
+          <t>SciFact=85.86;TRECCOVID=2.17;NFCorpus=17.92;SCIDOCS=21.39;LitSearch=63.63;QASA=32.31</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr"/>
@@ -11923,12 +11939,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LinerAI/embeddinggemma-300m-academic</t>
+          <t>LinerAI/snowflake-arctic-embed-m-v2.0-academic</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>embeddinggemma-300m-academic</t>
+          <t>snowflake-arctic-embed-m-v2.0-academic</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -11938,7 +11954,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://huggingface.co/LinerAI/embeddinggemma-300m-academic</t>
+          <t>https://huggingface.co/LinerAI/snowflake-arctic-embed-m-v2.0-academic</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11948,7 +11964,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>학술 검색 전용 파인튜닝된 경량 임베딩 모델로, LitSearch·QASA에서 원본 대비 향상된 학술 문헌 검색에 적합</t>
+          <t>학술 검색 전용 파인튜닝된 중형 임베딩 모델로 속도-성능 균형이 좋은 학술 문헌 검색에 적합</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -11968,7 +11984,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
@@ -11978,19 +11994,19 @@
         <v>45989</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>307581696</v>
+        <v>305368320</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>2048</v>
+        <v>4096</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Gemma3TextModel</t>
+          <t>GteModel</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12000,7 +12016,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>google/gemma-3-300m</t>
+          <t>Snowflake/snowflake-arctic-embed-m-v2.0</t>
         </is>
       </c>
       <c r="S128" t="inlineStr"/>
@@ -12010,7 +12026,7 @@
       <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
-          <t>SciFact=88.63;TRECCOVID=1.86;NFCorpus=17.35;SCIDOCS=18.79;LitSearch=62.50;QASA=36.90</t>
+          <t>SciFact=86.09;TRECCOVID=2.19;NFCorpus=17.70;SCIDOCS=21.29;LitSearch=64.35;QASA=32.10</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr"/>
@@ -12018,37 +12034,33 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LinerAI/snowflake-arctic-embed-l-v2.0-academic</t>
+          <t>learning-unit/L1-16B-A3B</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>snowflake-arctic-embed-l-v2.0-academic</t>
+          <t>L1-16B-A3B</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>라이너</t>
+          <t>러닝유닛</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://huggingface.co/LinerAI/snowflake-arctic-embed-l-v2.0-academic</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2205.13147</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/learning-unit/L1-16B-A3B</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>학술 검색 전용 파인튜닝으로 LitSearch·QASA 등에서 원본 대비 성능이 향상된 학술 문헌 검색용 임베딩</t>
+          <t>의료 도메인 특화, HealthBench-Consensus 최고점(93.50) 기록한 효율적 3B 활성 MoE 모델</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>보건·의료·헬스케어</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12058,7 +12070,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -12067,25 +12079,25 @@
         </is>
       </c>
       <c r="K129" s="2" t="n">
-        <v>45989</v>
+        <v>46120</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>45989</v>
+        <v>46122</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>567754752</v>
+        <v>16242181824</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>XLMRobertaModel</t>
+          <t>GravityMoEForCausalLM</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -12095,7 +12107,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Snowflake/snowflake-arctic-embed-l-v2.0</t>
+          <t>trillionlabs/Gravity-16B-A3B-Base</t>
         </is>
       </c>
       <c r="S129" t="inlineStr"/>
@@ -12105,7 +12117,7 @@
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
-          <t>SciFact=85.86;TRECCOVID=2.17;NFCorpus=17.92;SCIDOCS=21.39;LitSearch=63.63;QASA=32.31</t>
+          <t>PubMedQA=84.20;AttrBench=78.40;MedQA=85.50;CareQA=88.20;HeadQA=85.80;MedMCQA=76.70;MMLU-Pro(Health)=74.90;M-ARC=82.00;MetaMedQA=73.10;MedHallu=76.10;MedCalc=43.90;MedBullets-4opt=78.90;MedBullets-5opt=70.80;MedXpertQA-R=27.50;MedXpertQA-U=29.20;HealthBench-Consensus=93.50</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr"/>
@@ -12113,37 +12125,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LinerAI/snowflake-arctic-embed-m-v2.0-academic</t>
+          <t>rtzr/ko-gemma-2-9b-it</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>snowflake-arctic-embed-m-v2.0-academic</t>
+          <t>ko-gemma-2-9b-it</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>라이너</t>
+          <t>리턴제로</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://huggingface.co/LinerAI/snowflake-arctic-embed-m-v2.0-academic</t>
+          <t>https://huggingface.co/rtzr/ko-gemma-2-9b-it</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2205.13147</t>
+          <t>https://arxiv.org/abs/2305.18290</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>학술 검색 전용 파인튜닝된 중형 임베딩 모델로 속도-성능 균형이 좋은 학술 문헌 검색에 적합</t>
+          <t>LogicKor 전 항목에서 동급 한국어 모델 중 1위, 한국어 대화·질의응답에 적합</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12153,34 +12165,32 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K130" s="2" t="n">
-        <v>45989</v>
+        <v>45484</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>45989</v>
+        <v>45488</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>305368320</v>
-      </c>
-      <c r="N130" s="3" t="n">
-        <v>4096</v>
-      </c>
+        <v>9241705984</v>
+      </c>
+      <c r="N130" s="3" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>GteModel</t>
+          <t>Gemma2ForCausalLM</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -12190,80 +12200,86 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Snowflake/snowflake-arctic-embed-m-v2.0</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
+          <t>google/gemma-2-9b</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>LogicKor-Reasoning(단일)=9.14;LogicKor-Reasoning(멀티)=8.00;LogicKor-Writing(단일)=9.43;LogicKor-Writing(멀티)=9.29;LogicKor-Understanding(단일)=9.57;LogicKor-Understanding(멀티)=9.86;LogicKor-Grammar(단일)=7.14;LogicKor-Grammar(멀티)=5.00</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>LogicKor-Math(단일)=8.71;LogicKor-Math(멀티)=8.00;LogicKor-Coding(단일)=9.00;LogicKor-Coding(멀티)=9.43</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>SciFact=86.09;TRECCOVID=2.19;NFCorpus=17.70;SCIDOCS=21.29;LitSearch=64.35;QASA=32.10</t>
-        </is>
-      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>LogicKor-Math(단일)=8.71;LogicKor-Math(멀티)=8.00;LogicKor-Reasoning(단일)=9.14;LogicKor-Reasoning(멀티)=8.00;LogicKor-Writing(단일)=9.43;LogicKor-Writing(멀티)=9.29;LogicKor-Coding(단일)=9.00;LogicKor-Coding(멀티)=9.43;LogicKor-Understanding(단일)=9.57;LogicKor-Understanding(멀티)=9.86;LogicKor-Grammar(단일)=7.14;LogicKor-Grammar(멀티)=5.00</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>learning-unit/L1-16B-A3B</t>
+          <t>maum-ai/Llama-3.2-MAAL-11B-Vision-v0.1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>L1-16B-A3B</t>
+          <t>Llama-3.2-MAAL-11B-Vision-v0.1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>러닝유닛</t>
+          <t>마음AI</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://huggingface.co/learning-unit/L1-16B-A3B</t>
+          <t>https://huggingface.co/maum-ai/Llama-3.2-MAAL-11B-Vision-v0.1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>의료 도메인 특화, HealthBench-Consensus 최고점(93.50) 기록한 효율적 3B 활성 MoE 모델</t>
+          <t>한국어 VQA·OCR 특화, 기존 베이스 모델 대비 KOFFVQA 20% 성능 향상해 한국어 이미지 이해 업무에 적합</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>보건·의료·헬스케어</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>llama3.2</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
-        <v>46120</v>
+        <v>45615</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>46122</v>
+        <v>45632</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>16242181824</v>
-      </c>
-      <c r="N131" s="3" t="n">
-        <v>32768</v>
-      </c>
+        <v>10670220835</v>
+      </c>
+      <c r="N131" s="3" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>BF16</t>
@@ -12271,7 +12287,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>GravityMoEForCausalLM</t>
+          <t>MllamaForConditionalGeneration</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -12281,50 +12297,50 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>trillionlabs/Gravity-16B-A3B-Base</t>
+          <t>meta-llama/Llama-3.2-11B-Vision-Instruct</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>KOFFVQA=61.13</t>
+        </is>
+      </c>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>PubMedQA=84.20;AttrBench=78.40;MedQA=85.50;CareQA=88.20;HeadQA=85.80;MedMCQA=76.70;MMLU-Pro(Health)=74.90;M-ARC=82.00;MetaMedQA=73.10;MedHallu=76.10;MedCalc=43.90;MedBullets-4opt=78.90;MedBullets-5opt=70.80;MedXpertQA-R=27.50;MedXpertQA-U=29.20;HealthBench-Consensus=93.50</t>
-        </is>
-      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>KOFFVQA=61.13</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rtzr/ko-gemma-2-9b-it</t>
+          <t>maum-ai/Llama-3-MAAL-8B-Instruct-v0.1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ko-gemma-2-9b-it</t>
+          <t>Llama-3-MAAL-8B-Instruct-v0.1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>리턴제로</t>
+          <t>마음AI</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://huggingface.co/rtzr/ko-gemma-2-9b-it</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2305.18290</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/maum-ai/Llama-3-MAAL-8B-Instruct-v0.1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LogicKor 전 항목에서 동급 한국어 모델 중 1위, 한국어 대화·질의응답에 적합</t>
+          <t>영어→한국어 지시 전이 학습으로 LogicKor 평균 5.23점 동급 최고, 한국어 챗봇 활용에 적합</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -12339,22 +12355,22 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>llama3</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
-        <v>45484</v>
+        <v>45406</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>45488</v>
+        <v>45412</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>9241705984</v>
+        <v>8030269440</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" t="inlineStr">
@@ -12364,7 +12380,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gemma2ForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -12374,24 +12390,20 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>google/gemma-2-9b</t>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>LogicKor-Reasoning(단일)=9.14;LogicKor-Reasoning(멀티)=8.00;LogicKor-Writing(단일)=9.43;LogicKor-Writing(멀티)=9.29;LogicKor-Understanding(단일)=9.57;LogicKor-Understanding(멀티)=9.86;LogicKor-Grammar(단일)=7.14;LogicKor-Grammar(멀티)=5.00</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>LogicKor-Math(단일)=8.71;LogicKor-Math(멀티)=8.00;LogicKor-Coding(단일)=9.00;LogicKor-Coding(멀티)=9.43</t>
-        </is>
-      </c>
+          <t>LogicKor-single=5.80;LogicKor-multi=4.66;LogicKor=5.23</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr">
         <is>
-          <t>LogicKor-Math(단일)=8.71;LogicKor-Math(멀티)=8.00;LogicKor-Reasoning(단일)=9.14;LogicKor-Reasoning(멀티)=8.00;LogicKor-Writing(단일)=9.43;LogicKor-Writing(멀티)=9.29;LogicKor-Coding(단일)=9.00;LogicKor-Coding(멀티)=9.43;LogicKor-Understanding(단일)=9.57;LogicKor-Understanding(멀티)=9.86;LogicKor-Grammar(단일)=7.14;LogicKor-Grammar(멀티)=5.00</t>
+          <t>LogicKor-single=5.80;LogicKor-multi=4.66;LogicKor=5.23</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -12400,28 +12412,28 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>maum-ai/Llama-3.2-MAAL-11B-Vision-v0.1</t>
+          <t>MarkrAI/ksafeguard-8b</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Llama-3.2-MAAL-11B-Vision-v0.1</t>
+          <t>ksafeguard-8b</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>마음AI</t>
+          <t>마커에이아이</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://huggingface.co/maum-ai/Llama-3.2-MAAL-11B-Vision-v0.1</t>
+          <t>https://huggingface.co/MarkrAI/ksafeguard-8b</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>한국어 VQA·OCR 특화, 기존 베이스 모델 대비 KOFFVQA 20% 성능 향상해 한국어 이미지 이해 업무에 적합</t>
+          <t>한국어 관용표현 오탐(과탐)이 가장 적은 안전성 판별기로, FPR 0.124(공개 모델 중 최저)로 콘텐츠 모더레이션에 적합</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -12431,27 +12443,27 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Text, Image</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>llama3.2</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K133" s="2" t="n">
-        <v>45615</v>
+        <v>46206</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>45632</v>
+        <v>46206</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>10670220835</v>
+        <v>8030285824</v>
       </c>
       <c r="N133" s="3" t="inlineStr"/>
       <c r="O133" t="inlineStr">
@@ -12461,7 +12473,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>MllamaForConditionalGeneration</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -12471,50 +12483,46 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.2-11B-Vision-Instruct</t>
+          <t>kakaocorp/kanana-1.5-8b-instruct-2505</t>
         </is>
       </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>KOFFVQA=61.13</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>KOFFVQA=61.13</t>
-        </is>
-      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>WJ=98.3;WG-Prompt=95.4;WG-Refusal=96.0;WG-Resp=91.7;FR=91.7;K-OverRefusal-FPR=12.4</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>maum-ai/Llama-3-MAAL-8B-Instruct-v0.1</t>
+          <t>MarkrAI/kyujin-CoTy-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Llama-3-MAAL-8B-Instruct-v0.1</t>
+          <t>kyujin-CoTy-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>마음AI</t>
+          <t>마커에이아이</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://huggingface.co/maum-ai/Llama-3-MAAL-8B-Instruct-v0.1</t>
+          <t>https://huggingface.co/MarkrAI/kyujin-CoTy-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>영어→한국어 지시 전이 학습으로 LogicKor 평균 5.23점 동급 최고, 한국어 챗봇 활용에 적합</t>
+          <t>CoT 학습으로 Open Ko-LLM 리더보드 Ko-CommonGen V2 84.86점을 기록한 한국어 사고연쇄(CoT) 특화 모델</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -12529,32 +12537,32 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>llama3</t>
+          <t>cc-by-nc-sa-4.0</t>
         </is>
       </c>
       <c r="K134" s="2" t="n">
-        <v>45406</v>
+        <v>45202</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>45412</v>
+        <v>45776</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>8030269440</v>
+        <v>12893605120</v>
       </c>
       <c r="N134" s="3" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP16+FP32</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>GPTNeoXForCausalLM</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -12564,20 +12572,24 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+          <t>EleutherAI/polyglot-ko-12.8b</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>LogicKor-single=5.80;LogicKor-multi=4.66;LogicKor=5.23</t>
+          <t>Ko-ARC=34.98;Ko-HellaSwag=49.11;Ko-MMLU=25.68;Ko-CommonGen V2=84.86</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Ko-TruthfulQA=37.59</t>
+        </is>
+      </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>LogicKor-single=5.80;LogicKor-multi=4.66;LogicKor=5.23</t>
+          <t>Ko-CommonGen V2=84.86</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -12586,12 +12598,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MarkrAI/ksafeguard-8b</t>
+          <t>MarkrAI/kyujin-Poly-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ksafeguard-8b</t>
+          <t>kyujin-Poly-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -12601,13 +12613,13 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/ksafeguard-8b</t>
+          <t>https://huggingface.co/MarkrAI/kyujin-Poly-platypus-ko-12.8b</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>한국어 관용표현 오탐(과탐)이 가장 적은 안전성 판별기로, FPR 0.124(공개 모델 중 최저)로 콘텐츠 모더레이션에 적합</t>
+          <t>Ko-CommonGen V2 74.88, SentiNeg F1 95.97 등에서 강점을 보이는 한국어 파인튜닝 모델</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -12627,27 +12639,27 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>cc-by-nc-sa-4.0</t>
         </is>
       </c>
       <c r="K135" s="2" t="n">
-        <v>46206</v>
+        <v>45199</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>46206</v>
+        <v>45546</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>8030285824</v>
+        <v>12893605120</v>
       </c>
       <c r="N135" s="3" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP16+FP32</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>GPTNeoXForCausalLM</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -12657,30 +12669,42 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>kakaocorp/kanana-1.5-8b-instruct-2505</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr"/>
+          <t>EleutherAI/polyglot-ko-12.8b</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Ko-ARC=35.15;Ko-HellaSwag=50.39;Ko-MMLU=25.58;Ko-CommonGen V2=74.88;COPA(5-shot)=80.99;HellaSwag(5-shot)=48.58;BoolQ(5-shot)=65.20</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>WJ=98.3;WG-Prompt=95.4;WG-Refusal=96.0;WG-Resp=91.7;FR=91.7;K-OverRefusal-FPR=12.4</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
+          <t>Ko-TruthfulQA=38.74</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Ko-CommonGen V2=74.88</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>SentiNeg(5-shot)=95.97</t>
+        </is>
+      </c>
       <c r="Y135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MarkrAI/kyujin-CoTy-platypus-ko-12.8b</t>
+          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v2.1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kyujin-CoTy-platypus-ko-12.8b</t>
+          <t>RAG-KO-Mixtral-7Bx2-v2.1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -12690,13 +12714,13 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/kyujin-CoTy-platypus-ko-12.8b</t>
+          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v2.1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CoT 학습으로 Open Ko-LLM 리더보드 Ko-CommonGen V2 84.86점을 기록한 한국어 사고연쇄(CoT) 특화 모델</t>
+          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12720,23 +12744,23 @@
         </is>
       </c>
       <c r="K136" s="2" t="n">
-        <v>45202</v>
+        <v>45333</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>45776</v>
+        <v>45333</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>12893605120</v>
+        <v>12879138816</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>FP16+FP32</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>GPTNeoXForCausalLM</t>
+          <t>MixtralForCausalLM</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -12746,38 +12770,26 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>EleutherAI/polyglot-ko-12.8b</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Ko-ARC=34.98;Ko-HellaSwag=49.11;Ko-MMLU=25.68;Ko-CommonGen V2=84.86</t>
-        </is>
-      </c>
+          <t>DopeorNope/Ko-Mixtral-v1.4-MoE-7Bx2</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>Ko-TruthfulQA=37.59</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>Ko-CommonGen V2=84.86</t>
-        </is>
-      </c>
+      <c r="V136" t="inlineStr"/>
+      <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MarkrAI/kyujin-Poly-platypus-ko-12.8b</t>
+          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v2.0</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kyujin-Poly-platypus-ko-12.8b</t>
+          <t>RAG-KO-Mixtral-7Bx2-v2.0</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -12787,13 +12799,13 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/kyujin-Poly-platypus-ko-12.8b</t>
+          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v2.0</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ko-CommonGen V2 74.88, SentiNeg F1 95.97 등에서 강점을 보이는 한국어 파인튜닝 모델</t>
+          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12817,23 +12829,23 @@
         </is>
       </c>
       <c r="K137" s="2" t="n">
-        <v>45199</v>
+        <v>45328</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>45546</v>
+        <v>45330</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>12893605120</v>
+        <v>12879138816</v>
       </c>
       <c r="N137" s="3" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>FP16+FP32</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>GPTNeoXForCausalLM</t>
+          <t>MixtralForCausalLM</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -12843,42 +12855,26 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>EleutherAI/polyglot-ko-12.8b</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Ko-ARC=35.15;Ko-HellaSwag=50.39;Ko-MMLU=25.58;Ko-CommonGen V2=74.88;COPA(5-shot)=80.99;HellaSwag(5-shot)=48.58;BoolQ(5-shot)=65.20</t>
-        </is>
-      </c>
+          <t>DopeorNope/Ko-Mixtral-v1.4-MoE-7Bx2</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>Ko-TruthfulQA=38.74</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>Ko-CommonGen V2=74.88</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>SentiNeg(5-shot)=95.97</t>
-        </is>
-      </c>
+      <c r="V137" t="inlineStr"/>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v2.1</t>
+          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v1.1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RAG-KO-Mixtral-7Bx2-v2.1</t>
+          <t>RAG-KO-Mixtral-7Bx2-v1.1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -12888,7 +12884,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v2.1</t>
+          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v1.1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -12918,10 +12914,10 @@
         </is>
       </c>
       <c r="K138" s="2" t="n">
-        <v>45333</v>
+        <v>45320</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>45333</v>
+        <v>45327</v>
       </c>
       <c r="M138" s="3" t="n">
         <v>12879138816</v>
@@ -12944,7 +12940,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>DopeorNope/Ko-Mixtral-v1.4-MoE-7Bx2</t>
+          <t>DopeorNope/Ko-Mixtral-v1.3-MoE-7Bx2</t>
         </is>
       </c>
       <c r="S138" t="inlineStr"/>
@@ -12958,12 +12954,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v2.0</t>
+          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v1.15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RAG-KO-Mixtral-7Bx2-v2.0</t>
+          <t>RAG-KO-Mixtral-7Bx2-v1.15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12973,7 +12969,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v2.0</t>
+          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v1.15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -13003,10 +12999,10 @@
         </is>
       </c>
       <c r="K139" s="2" t="n">
-        <v>45328</v>
+        <v>45323</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>45330</v>
+        <v>45323</v>
       </c>
       <c r="M139" s="3" t="n">
         <v>12879138816</v>
@@ -13029,7 +13025,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>DopeorNope/Ko-Mixtral-v1.4-MoE-7Bx2</t>
+          <t>DopeorNope/Ko-Mixtral-v1.3-MoE-7Bx2</t>
         </is>
       </c>
       <c r="S139" t="inlineStr"/>
@@ -13043,83 +13039,75 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v1.1</t>
+          <t>Motif-Technologies/motif-vae</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RAG-KO-Mixtral-7Bx2-v1.1</t>
+          <t>motif-vae</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>마커에이아이</t>
+          <t>모티프 테크놀로지스</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v1.1</t>
+          <t>https://huggingface.co/Motif-Technologies/motif-vae</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>동급 32x VAE 중 문서 텍스트 재현력(OCR-NED)이 최고 수준으로 텍스트가 많은 영상·이미지 압축에 적합</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>한국어</t>
-        </is>
-      </c>
+          <t>Image, Video</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>cc-by-nc-sa-4.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="K140" s="2" t="n">
-        <v>45320</v>
+        <v>46185</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>45327</v>
+        <v>46199</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>12879138816</v>
+        <v>1243812899</v>
       </c>
       <c r="N140" s="3" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>FP16</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>MixtralForCausalLM</t>
-        </is>
-      </c>
+          <t>FP32</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>DopeorNope/Ko-Mixtral-v1.3-MoE-7Bx2</t>
-        </is>
-      </c>
+          <t>베이스 모델(프롬스크래치 사전학습)</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>ImageNet PSNR=30.27;ImageNet SSIM=0.852;FFHQ PSNR=36.17;FFHQ SSIM=0.921;OmniDoc SSIM=0.849;OmniDoc PSNR=22.4;OmniDoc LPIPS=0.052;OmniDoc FID=3.43;OmniDoc OCR-NED=0.825;Kinetics-400 PSNR=35.37;Kinetics-400 SSIM=0.954;Kinetics-400 LPIPS=0.046;OpenVid PSNR=36.96;OpenVid SSIM=0.953;OpenVid LPIPS=0.04;UCF101 FVD@250K=276</t>
+        </is>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
@@ -13128,83 +13116,83 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MarkrAI/RAG-KO-Mixtral-7Bx2-v1.15</t>
+          <t>Motif-Technologies/Motif-Video-2B</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RAG-KO-Mixtral-7Bx2-v1.15</t>
+          <t>Motif-Video-2B</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>마커에이아이</t>
+          <t>모티프 테크놀로지스</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://huggingface.co/MarkrAI/RAG-KO-Mixtral-7Bx2-v1.15</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>https://huggingface.co/Motif-Technologies/Motif-Video-2B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.16503</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>VBench 83.76%로 오픈소스 중 최고 성능, Wan2.1-14B 대비 파라미터 7배 적어 효율적 영상생성에 적합</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image, Video</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>cc-by-nc-sa-4.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K141" s="2" t="n">
-        <v>45323</v>
+        <v>46126</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>45323</v>
+        <v>46157</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>12879138816</v>
+        <v>2037809600</v>
       </c>
       <c r="N141" s="3" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>FP16</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>MixtralForCausalLM</t>
-        </is>
-      </c>
+          <t>FP32</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>DopeorNope/Ko-Mixtral-v1.3-MoE-7Bx2</t>
-        </is>
-      </c>
+          <t>베이스 모델(프롬스크래치 사전학습)</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>VBench Total=83.76;VBench Quality=84.59;VBench Semantic=80.44;VBench Spatial Relationship=83.02;VBench Object Class=92.93;VBench Multiple Objects=77.29;VBench Imaging Quality=70.5</t>
+        </is>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
@@ -13213,12 +13201,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Motif-Technologies/motif-vae</t>
+          <t>Motif-Technologies/Motif-Video-2B-GGUF</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>motif-vae</t>
+          <t>Motif-Video-2B-GGUF</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -13228,13 +13216,13 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/motif-vae</t>
+          <t>https://huggingface.co/Motif-Technologies/Motif-Video-2B-GGUF</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>동급 32x VAE 중 문서 텍스트 재현력(OCR-NED)이 최고 수준으로 텍스트가 많은 영상·이미지 압축에 적합</t>
+          <t>GGUF 양자화로 VRAM 최대 2.7GB 절감, 속도 저하 없이 경량 배포 가능</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -13244,44 +13232,48 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Image, Video</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>Text, Video</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>영어</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K142" s="2" t="n">
-        <v>46185</v>
+        <v>46135</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>46199</v>
+        <v>46157</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>1243812899</v>
+        <v>2000000000</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>FP32</t>
+          <t>GGUF(양자화)</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Motif-Technologies/Motif-Video-2B</t>
+        </is>
+      </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>ImageNet PSNR=30.27;ImageNet SSIM=0.852;FFHQ PSNR=36.17;FFHQ SSIM=0.921;OmniDoc SSIM=0.849;OmniDoc PSNR=22.4;OmniDoc LPIPS=0.052;OmniDoc FID=3.43;OmniDoc OCR-NED=0.825;Kinetics-400 PSNR=35.37;Kinetics-400 SSIM=0.954;Kinetics-400 LPIPS=0.046;OpenVid PSNR=36.96;OpenVid SSIM=0.953;OpenVid LPIPS=0.04;UCF101 FVD@250K=276</t>
-        </is>
-      </c>
+      <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
@@ -13290,12 +13282,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-Video-2B</t>
+          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Motif-Video-2B</t>
+          <t>Motif-2-12.7B-Base</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -13305,32 +13297,32 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-Video-2B</t>
+          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Base</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2604.16503</t>
+          <t>https://arxiv.org/abs/2511.07464</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>VBench 83.76%로 오픈소스 중 최고 성능, Wan2.1-14B 대비 파라미터 7배 적어 효율적 영상생성에 적합</t>
+          <t>수학(MATH 73.62)·코딩(MBPP 81.5)에서 동급 모델 대비 우수해 수학·코딩 특화 작업에 적합</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Text, Image, Video</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -13339,13 +13331,13 @@
         </is>
       </c>
       <c r="K143" s="2" t="n">
-        <v>46126</v>
+        <v>45950</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>46157</v>
+        <v>46091</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>2037809600</v>
+        <v>12703860896</v>
       </c>
       <c r="N143" s="3" t="inlineStr"/>
       <c r="O143" t="inlineStr">
@@ -13353,20 +13345,28 @@
           <t>FP32</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>MotifForCausalLM</t>
+        </is>
+      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>베이스 모델(프롬스크래치 사전학습)</t>
         </is>
       </c>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>VBench Total=83.76;VBench Quality=84.59;VBench Semantic=80.44;VBench Spatial Relationship=83.02;VBench Object Class=92.93;VBench Multiple Objects=77.29;VBench Imaging Quality=70.5</t>
-        </is>
-      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>MMLU=78.1;MMLU-Redux=78.68;MMLU-Pro=66.38;SuperGPQA=32.68;BBH=81.34;GPQA=42.18;GPQA-Diamond=42.92;DROP=69.9;HellaSwag=84;BoolQ=78.5;PIQA=81.6;SIQA=53.8;TriviaQA=72.2;Natural Question=29.6;ARC-C=69.6;ARC-E=84.1;WinoGrande=79.6</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>GSM8K(4-shot)=93.85;GSM8K(8-shot)=94.92;MATH=73.62;EvalPlus=72.22;MBPP=81.5;CRUX-O=63.1;HumanEval=65.9</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
@@ -13375,12 +13375,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-Video-2B-GGUF</t>
+          <t>Motif-Technologies/Motif-2-12.7B-Instruct</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Motif-Video-2B-GGUF</t>
+          <t>Motif-2-12.7B-Instruct</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -13390,28 +13390,32 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-Video-2B-GGUF</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Instruct</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.07464</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GGUF 양자화로 VRAM 최대 2.7GB 절감, 속도 저하 없이 경량 배포 가능</t>
+          <t>수학(MATH 97)·코딩(MBPP 91) 성능이 우수해 수학·코딩 특화 챗봇 용도에 적합</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Text, Video</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -13420,48 +13424,66 @@
         </is>
       </c>
       <c r="K144" s="2" t="n">
-        <v>46135</v>
+        <v>45960</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>46157</v>
+        <v>46091</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>2000000000</v>
-      </c>
-      <c r="N144" s="3" t="inlineStr"/>
+        <v>12703860896</v>
+      </c>
+      <c r="N144" s="3" t="n">
+        <v>32768</v>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>GGUF(양자화)</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr"/>
+          <t>FP32</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>MotifForCausalLM</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-Video-2B</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
+          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>MMLU=86.11;MMLU-Redux=90.02;BBH=85.78;GPQA-Diamond=63.6;IFEval(strict)=75.78;IFEval(0-shot)=76.52;ZebraLogic=69.5</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>GSM8K=96.13;MATH=97;MBPP=91;MATH-500=96.8;AIME24=72.3;AIME25=63.6;BFCL v3=55.34;LiveCodeBench v5=50.03;LiveCodeBench v5(CoT)=61.66;HumanEval=93.2</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>LiveBench 2024-11-25=33.8</t>
+        </is>
+      </c>
       <c r="Y144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
+          <t>Motif-Technologies/Motif-2-12.7B-Reasoning</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Motif-2-12.7B-Base</t>
+          <t>Motif-2-12.7B-Reasoning</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -13471,17 +13493,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Base</t>
+          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Reasoning</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.07464</t>
+          <t>https://arxiv.org/abs/2309.00071</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>수학(MATH 73.62)·코딩(MBPP 81.5)에서 동급 모델 대비 우수해 수학·코딩 특화 작업에 적합</t>
+          <t>추론 강화판으로 AIME24(88.3)·수학(MATH-500 99.3) 성능이 크게 향상돼 고난도 추론 작업에 적합</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -13505,7 +13527,7 @@
         </is>
       </c>
       <c r="K145" s="2" t="n">
-        <v>45950</v>
+        <v>45989</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>46091</v>
@@ -13513,7 +13535,9 @@
       <c r="M145" s="3" t="n">
         <v>12703860896</v>
       </c>
-      <c r="N145" s="3" t="inlineStr"/>
+      <c r="N145" s="3" t="n">
+        <v>65536</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>FP32</t>
@@ -13526,35 +13550,43 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr"/>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
+        </is>
+      </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>MMLU=78.1;MMLU-Redux=78.68;MMLU-Pro=66.38;SuperGPQA=32.68;BBH=81.34;GPQA=42.18;GPQA-Diamond=42.92;DROP=69.9;HellaSwag=84;BoolQ=78.5;PIQA=81.6;SIQA=53.8;TriviaQA=72.2;Natural Question=29.6;ARC-C=69.6;ARC-E=84.1;WinoGrande=79.6</t>
+          <t>MMLU=84.07;MMLU-Redux=88.89;BBH=78.34;GPQA-Diamond=70;IFEval(strict)=79.11;IFEval(0-shot)=81.89;ZebraLogic=77</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>GSM8K(4-shot)=93.85;GSM8K(8-shot)=94.92;MATH=73.62;EvalPlus=72.22;MBPP=81.5;CRUX-O=63.1;HumanEval=65.9</t>
+          <t>GSM8K=95.53;MATH=95.07;MBPP=88.9;MATH-500=99.3;AIME24=88.3;AIME25=80;BFCL v3=60.2;LiveCodeBench v5=65;LiveCodeBench v5(CoT)=60.1;HumanEval=93.2</t>
         </is>
       </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>LiveBench 2024-11-25=49.9</t>
+        </is>
+      </c>
       <c r="Y145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2-12.7B-Instruct</t>
+          <t>Motif-Technologies/Motif-2.6B</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Motif-2-12.7B-Instruct</t>
+          <t>Motif-2.6B</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -13564,17 +13596,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Instruct</t>
+          <t>https://huggingface.co/Motif-Technologies/Motif-2.6B</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2511.07464</t>
+          <t>https://arxiv.org/abs/2508.09148</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>수학(MATH 97)·코딩(MBPP 91) 성능이 우수해 수학·코딩 특화 챗봇 용도에 적합</t>
+          <t>미스트랄 7B 대비 코딩(HumanEval +123.93%)·수학(MATH +206.87%)에서 크게 앞서는 경량 언어모델</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -13598,17 +13630,15 @@
         </is>
       </c>
       <c r="K146" s="2" t="n">
-        <v>45960</v>
+        <v>45814</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>46091</v>
+        <v>45897</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>12703860896</v>
-      </c>
-      <c r="N146" s="3" t="n">
-        <v>32768</v>
-      </c>
+        <v>2597218432</v>
+      </c>
+      <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>FP32</t>
@@ -13621,43 +13651,39 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
-        </is>
-      </c>
+          <t>베이스 모델(프롬스크래치 사전학습)</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
-          <t>MMLU=86.11;MMLU-Redux=90.02;BBH=85.78;GPQA-Diamond=63.6;IFEval(strict)=75.78;IFEval(0-shot)=76.52;ZebraLogic=69.5</t>
+          <t>MMLU=57.93;MMLU-Redux=59.54;MMLU-Pro=28.4;MMLU-stem=52.9;HellaSwag=61.35;WinoGrande=59.91;PIQA=75.95;ARC-E=87.21;ARC-C=74.2;BBH=48.56;BoolQ=67.76;SIQA=61.97;TriviaQA=54.97;NQ=11.14;GPQA=18.53;GPQA-Diamond=31.81;ANLI=47.99;CommonSenseQA=71.25;OpenBookQA=87.8;MT-Bench=6.77;IFEval=74.02;DROP=29.33;MedQA=42.1</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>GSM8K=96.13;MATH=97;MBPP=91;MATH-500=96.8;AIME24=72.3;AIME25=63.6;BFCL v3=55.34;LiveCodeBench v5=50.03;LiveCodeBench v5(CoT)=61.66;HumanEval=93.2</t>
+          <t>MATH=40.2;GSM8K=75.66;HumanEval=68.3;MBPP=60.3;HumanEval+=62.2;MBPP+=50.8</t>
         </is>
       </c>
       <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>TruthfulQA=52.07</t>
+        </is>
+      </c>
       <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>LiveBench 2024-11-25=33.8</t>
-        </is>
-      </c>
+      <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2-12.7B-Reasoning</t>
+          <t>Motif-Technologies/Motif-2.6b-v1.1-LC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Motif-2-12.7B-Reasoning</t>
+          <t>Motif-2.6b-v1.1-LC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -13667,17 +13693,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-2-12.7B-Reasoning</t>
+          <t>https://huggingface.co/Motif-Technologies/Motif-2.6b-v1.1-LC</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2309.00071</t>
+          <t>https://arxiv.org/abs/2508.09148</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>추론 강화판으로 AIME24(88.3)·수학(MATH-500 99.3) 성능이 크게 향상돼 고난도 추론 작업에 적합</t>
+          <t>Motif-2.6B 대비 16K 컨텍스트 지원, GPQA(+46.97%) 성능 대폭 향상으로 장문 처리에 적합</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -13697,20 +13723,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="K147" s="2" t="n">
-        <v>45989</v>
+        <v>45859</v>
       </c>
       <c r="L147" s="2" t="n">
-        <v>46091</v>
+        <v>45887</v>
       </c>
       <c r="M147" s="3" t="n">
-        <v>12703860896</v>
+        <v>2597218432</v>
       </c>
       <c r="N147" s="3" t="n">
-        <v>65536</v>
+        <v>16384</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -13729,58 +13755,54 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2-12.7B-Base</t>
+          <t>Motif-Technologies/Motif-2.6B</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>MMLU=84.07;MMLU-Redux=88.89;BBH=78.34;GPQA-Diamond=70;IFEval(strict)=79.11;IFEval(0-shot)=81.89;ZebraLogic=77</t>
+          <t>MMLU=58.7;MMLU-Pro=32.0;WinoGrande=60.3;ARC-E=84.7;ARC-C=73.0;SIQA=63.3;BoolQ=71.0;AGIEval=31.0;GPQA=27.23</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>GSM8K=95.53;MATH=95.07;MBPP=88.9;MATH-500=99.3;AIME24=88.3;AIME25=80;BFCL v3=60.2;LiveCodeBench v5=65;LiveCodeBench v5(CoT)=60.1;HumanEval=93.2</t>
+          <t>MATH=47.3;GSM8K=80.3;HumanEval=70.1</t>
         </is>
       </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>LiveBench 2024-11-25=49.9</t>
-        </is>
-      </c>
+      <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2.6B</t>
+          <t>vaiv/GeM2-Llamion-14B-Base</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Motif-2.6B</t>
+          <t>GeM2-Llamion-14B-Base</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>모티프 테크놀로지스</t>
+          <t>바이브컴퍼니</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-2.6B</t>
+          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-Base</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.09148</t>
+          <t>https://arxiv.org/abs/2605.25676</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>미스트랄 7B 대비 코딩(HumanEval +123.93%)·수학(MATH +206.87%)에서 크게 앞서는 경량 언어모델</t>
+          <t>Orion-14B-Base를 파라미터 매핑으로 LLaMA 아키텍처로 변환, 재학습 없이 호환성 확보</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13795,7 +13817,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -13804,47 +13826,39 @@
         </is>
       </c>
       <c r="K148" s="2" t="n">
-        <v>45814</v>
+        <v>45425</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>45897</v>
+        <v>46168</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>2597218432</v>
+        <v>14498288640</v>
       </c>
       <c r="N148" s="3" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
-          <t>FP32</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>MotifForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>MMLU=57.93;MMLU-Redux=59.54;MMLU-Pro=28.4;MMLU-stem=52.9;HellaSwag=61.35;WinoGrande=59.91;PIQA=75.95;ARC-E=87.21;ARC-C=74.2;BBH=48.56;BoolQ=67.76;SIQA=61.97;TriviaQA=54.97;NQ=11.14;GPQA=18.53;GPQA-Diamond=31.81;ANLI=47.99;CommonSenseQA=71.25;OpenBookQA=87.8;MT-Bench=6.77;IFEval=74.02;DROP=29.33;MedQA=42.1</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>MATH=40.2;GSM8K=75.66;HumanEval=68.3;MBPP=60.3;HumanEval+=62.2;MBPP+=50.8</t>
-        </is>
-      </c>
+          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>OrionStarAI/Orion-14B-Base</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>TruthfulQA=52.07</t>
-        </is>
-      </c>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
@@ -13852,32 +13866,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2.6b-v1.1-LC</t>
+          <t>vaiv/GeM2-Llamion-14B-Chat</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Motif-2.6b-v1.1-LC</t>
+          <t>GeM2-Llamion-14B-Chat</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>모티프 테크놀로지스</t>
+          <t>바이브컴퍼니</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Motif-Technologies/Motif-2.6b-v1.1-LC</t>
+          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-Chat</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.09148</t>
+          <t>https://arxiv.org/abs/2605.25676</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Motif-2.6B 대비 16K 컨텍스트 지원, GPQA(+46.97%) 성능 대폭 향상으로 장문 처리에 적합</t>
+          <t>Orion-14B-Chat을 파라미터 매핑으로 LLaMA 아키텍처로 변환한 대화형 모델, 재학습 없이 호환성 확보</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -13892,56 +13906,46 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K149" s="2" t="n">
-        <v>45859</v>
+        <v>45425</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>45887</v>
+        <v>46168</v>
       </c>
       <c r="M149" s="3" t="n">
-        <v>2597218432</v>
-      </c>
-      <c r="N149" s="3" t="n">
-        <v>16384</v>
-      </c>
+        <v>14498288640</v>
+      </c>
+      <c r="N149" s="3" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>FP32</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>MotifForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Motif-Technologies/Motif-2.6B</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>MMLU=58.7;MMLU-Pro=32.0;WinoGrande=60.3;ARC-E=84.7;ARC-C=73.0;SIQA=63.3;BoolQ=71.0;AGIEval=31.0;GPQA=27.23</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>MATH=47.3;GSM8K=80.3;HumanEval=70.1</t>
-        </is>
-      </c>
+          <t>OrionStarAI/Orion-14B-Chat</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr"/>
@@ -13951,12 +13955,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vaiv/GeM2-Llamion-14B-Base</t>
+          <t>vaiv/GeM2-Llamion-14B-LongChat</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>GeM2-Llamion-14B-Base</t>
+          <t>GeM2-Llamion-14B-LongChat</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -13966,7 +13970,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-Base</t>
+          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-LongChat</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13976,7 +13980,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Orion-14B-Base를 파라미터 매핑으로 LLaMA 아키텍처로 변환, 재학습 없이 호환성 확보</t>
+          <t>Orion-14B-LongChat 포팅 모델로 최대 200K 토큰 초장문 컨텍스트 지원, 장문 처리에 적합</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -14000,7 +14004,7 @@
         </is>
       </c>
       <c r="K150" s="2" t="n">
-        <v>45425</v>
+        <v>45441</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>46168</v>
@@ -14008,7 +14012,9 @@
       <c r="M150" s="3" t="n">
         <v>14498288640</v>
       </c>
-      <c r="N150" s="3" t="inlineStr"/>
+      <c r="N150" s="3" t="n">
+        <v>204800</v>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>BF16</t>
@@ -14026,7 +14032,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>OrionStarAI/Orion-14B-Base</t>
+          <t>OrionStarAI/Orion-14B-LongChat</t>
         </is>
       </c>
       <c r="S150" t="inlineStr"/>
@@ -14040,12 +14046,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>vaiv/GeM2-Llamion-14B-Chat</t>
+          <t>vaiv/kobigbird-roberta-large</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>GeM2-Llamion-14B-Chat</t>
+          <t>kobigbird-roberta-large</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -14055,17 +14061,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-Chat</t>
+          <t>https://huggingface.co/vaiv/kobigbird-roberta-large</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2605.25676</t>
+          <t>https://arxiv.org/abs/2309.10339</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Orion-14B-Chat을 파라미터 매핑으로 LLaMA 아키텍처로 변환한 대화형 모델, 재학습 없이 호환성 확보</t>
+          <t>klue/roberta-large 파라미터를 계승한 BigBird 구조로 긴 입력 길이의 한국어 문서 처리에 적합</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14080,42 +14086,42 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC-BY-SA-4.0</t>
         </is>
       </c>
       <c r="K151" s="2" t="n">
-        <v>45425</v>
+        <v>45175</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>46168</v>
+        <v>45197</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>14498288640</v>
+        <v>341413120</v>
       </c>
       <c r="N151" s="3" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP32+I64</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>BigBirdForMaskedLM</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>OrionStarAI/Orion-14B-Chat</t>
+          <t>klue/roberta-large</t>
         </is>
       </c>
       <c r="S151" t="inlineStr"/>
@@ -14129,32 +14135,28 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>vaiv/GeM2-Llamion-14B-LongChat</t>
+          <t>sionic-ai/comsat-embed-ja-0.3b-preview</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GeM2-Llamion-14B-LongChat</t>
+          <t>comsat-embed-ja-0.3b-preview</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>바이브컴퍼니</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://huggingface.co/vaiv/GeM2-Llamion-14B-LongChat</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2605.25676</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/sionic-ai/comsat-embed-ja-0.3b-preview</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Orion-14B-LongChat 포팅 모델로 최대 200K 토큰 초장문 컨텍스트 지원, 장문 처리에 적합</t>
+          <t>0.3B 경량 모델로 JMTEB 11개 태스크에서 4B 이하 중 최고 NDCG@10, 저지연 검색에 적합</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -14169,44 +14171,40 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K152" s="2" t="n">
-        <v>45441</v>
+        <v>46205</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>46168</v>
+        <v>46208</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>14498288640</v>
+        <v>314611968</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>204800</v>
+        <v>8192</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP32</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
-        </is>
-      </c>
+          <t>ModernBertModel</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>OrionStarAI/Orion-14B-LongChat</t>
+          <t>cl-nagoya/ruri-v3-310m</t>
         </is>
       </c>
       <c r="S152" t="inlineStr"/>
@@ -14220,32 +14218,28 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>vaiv/kobigbird-roberta-large</t>
+          <t>sionic-ai/comsat-embed-ja-8b-preview</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kobigbird-roberta-large</t>
+          <t>comsat-embed-ja-8b-preview</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>바이브컴퍼니</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://huggingface.co/vaiv/kobigbird-roberta-large</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2309.10339</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/sionic-ai/comsat-embed-ja-8b-preview</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>klue/roberta-large 파라미터를 계승한 BigBird 구조로 긴 입력 길이의 한국어 문서 처리에 적합</t>
+          <t>JMTEB(v2) 11개 태스크 평균 NDCG@10 0.8133로 비교 모델 중 최고, 일본어 검색에 적합</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -14260,42 +14254,40 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>영어, 일본어</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>CC-BY-SA-4.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K153" s="2" t="n">
-        <v>45175</v>
+        <v>46206</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>45197</v>
+        <v>46208</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>341413120</v>
-      </c>
-      <c r="N153" s="3" t="inlineStr"/>
+        <v>7567295488</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>8192</v>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>FP32+I64</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>BigBirdForMaskedLM</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
+          <t>Qwen3Model</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
-          <t>klue/roberta-large</t>
+          <t>Qwen/Qwen3-Embedding-8B</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
@@ -14309,32 +14301,28 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SamsungSDS-Research/SGuard-JailbreakFilter-2B-v1</t>
+          <t>sionic-ai/comsat-embed-ko-8b-preview</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SGuard-JailbreakFilter-2B-v1</t>
+          <t>comsat-embed-ko-8b-preview</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>삼성SDS 리서치</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://huggingface.co/SamsungSDS-Research/SGuard-JailbreakFilter-2B-v1</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2511.12497</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/sionic-ai/comsat-embed-ko-8b-preview</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>60여 종 탈옥 공격을 포괄하며 한/영 평균 F1 0.86/0.85로 상용 API보다 우수해 LLM 탈옥 방어 필터에 적합</t>
+          <t>MTEB 한국어 검색 9개 태스크 평균 NDCG@10 0.7930으로 비교 모델 중 최고, 한국어 검색에 적합</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -14354,20 +14342,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K154" s="2" t="n">
-        <v>45972</v>
+        <v>46205</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>46006</v>
+        <v>46208</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>2533539840</v>
+        <v>7567295488</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>131072</v>
+        <v>8192</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -14376,27 +14364,19 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>GraniteForCausalLM</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
+          <t>Qwen3Model</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ibm-granite/granite-3.3-2b-instruct</t>
+          <t>Qwen/Qwen3-Embedding-8B</t>
         </is>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>StrongREJECT_ko=79;Detect-Jailbreak_ko=84;StrongREJECT_en=84;Detect-Jailbreak_en=77</t>
-        </is>
-      </c>
+      <c r="V154" t="inlineStr"/>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
@@ -14404,32 +14384,28 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SamsungSDS-Research/SGuard-ContentFilter-2B-v1</t>
+          <t>sionic-ai/bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SGuard-ContentFilter-2B-v1</t>
+          <t>bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>삼성SDS 리서치</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://huggingface.co/SamsungSDS-Research/SGuard-ContentFilter-2B-v1</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2511.12497</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/sionic-ai/bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>경량 2B로 안전성 평가 F1 0.83, Llama-Guard-4-12B(0.62)보다 우수해 저비용 콘텐츠 필터링에 적합</t>
+          <t>AWQ 4bit 양자화로 인코딩 속도 약 60% 향상, 검색 성능은 유지해 저지연 배포에 적합</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14442,56 +14418,46 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>한국어, 영어</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K155" s="2" t="n">
-        <v>45972</v>
+        <v>45927</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>45986</v>
+        <v>45928</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>2533560320</v>
-      </c>
-      <c r="N155" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>8190735360</v>
+      </c>
+      <c r="N155" s="3" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP32+I32</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>GraniteForCausalLM</t>
+          <t>Qwen3ForCausalLM</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ibm-granite/granite-3.3-2b-instruct</t>
+          <t>BAAI/bge-reasoner-embed-qwen3-8b-0923</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>Beavertails=83;HarmfulQA=92;OpenAI Moderation=74;ToxicChat=72;XSTest=94</t>
-        </is>
-      </c>
+      <c r="V155" t="inlineStr"/>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
@@ -14499,28 +14465,28 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>saltlux/Ko-Llama3-Luxia-8B</t>
+          <t>sionic-ai/ko-gemma-2-9b-it-Q4_0-GGUF</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ko-Llama3-Luxia-8B</t>
+          <t>ko-gemma-2-9b-it-Q4_0-GGUF</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>솔트룩스</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://huggingface.co/saltlux/Ko-Llama3-Luxia-8B</t>
+          <t>https://huggingface.co/sionic-ai/ko-gemma-2-9b-it-Q4_0-GGUF</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Llama-3-8B를 한국어 100GB 코퍼스로 추가 사전학습, 한국어 자연어 생성에 특화</t>
+          <t>GGUF(Q4_0) 양자화로 llama.cpp에서 가볍게 구동되는 한국어 Gemma-2-9B 배포판</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -14535,44 +14501,38 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>llama3</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K156" s="2" t="n">
-        <v>45412</v>
+        <v>45517</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>45419</v>
+        <v>45517</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>8173916160</v>
-      </c>
-      <c r="N156" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>9000000000</v>
+      </c>
+      <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
-          <t>BF16</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>LlamaForCausalLM</t>
-        </is>
-      </c>
+          <t>GGUF(양자화)</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Llama-3-8B</t>
+          <t>rtzr/ko-gemma-2-9b-it</t>
         </is>
       </c>
       <c r="S156" t="inlineStr"/>
@@ -14586,68 +14546,78 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Supertone/supertonic-3</t>
+          <t>sionic-ai/nllb-200-ko-gec-3.3B</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>supertonic-3</t>
+          <t>nllb-200-ko-gec-3.3B</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>수퍼톤</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Supertone/supertonic-3</t>
+          <t>https://huggingface.co/sionic-ai/nllb-200-ko-gec-3.3B</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>31개 언어를 지원하는 99M 경량 온디바이스 TTS로 GPU 없이도 빠르게 동작해 로컬·엣지 배포에 적합</t>
+          <t>facebook/nllb-200-3.3B를 파인튜닝한 한국어 문법 교정 특화 모델(한국어 그래멀리)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Text, Audio</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>다국어(31개 언어)</t>
+          <t>다국어(196개 언어)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>OpenRAIL</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K157" s="2" t="n">
-        <v>46148</v>
+        <v>45470</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>46160</v>
+        <v>45475</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>99000000</v>
-      </c>
-      <c r="N157" s="3" t="inlineStr"/>
+        <v>3300000000</v>
+      </c>
+      <c r="N157" s="3" t="n">
+        <v>512</v>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Onnx</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
+          <t>M2M100ForConditionalGeneration</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>facebook/nllb-200-3.3B</t>
+        </is>
+      </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
@@ -14659,72 +14629,94 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Supertone/supertonic-2</t>
+          <t>SamsungSDS-Research/SGuard-JailbreakFilter-2B-v1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>supertonic-2</t>
+          <t>SGuard-JailbreakFilter-2B-v1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>수퍼톤</t>
+          <t>삼성SDS 리서치</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Supertone/supertonic-2</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>https://huggingface.co/SamsungSDS-Research/SGuard-JailbreakFilter-2B-v1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.12497</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>온디바이스 TTS로 실시간 대비 최대 167배 빠르고 66M 경량 파라미터라 엣지·모바일 배포에 적합</t>
+          <t>60여 종 탈옥 공격을 포괄하며 한/영 평균 F1 0.86/0.85로 상용 API보다 우수해 LLM 탈옥 방어 필터에 적합</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Text, Audio</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>다국어(5개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>OpenRAIL</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K158" s="2" t="n">
-        <v>46028</v>
+        <v>45972</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>46028</v>
+        <v>46006</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="N158" s="3" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+        <v>2533539840</v>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>131072</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>BF16</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Onnx</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
+          <t>GraniteForCausalLM</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>ibm-granite/granite-3.3-2b-instruct</t>
+        </is>
+      </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>StrongREJECT_ko=79;Detect-Jailbreak_ko=84;StrongREJECT_en=84;Detect-Jailbreak_en=77</t>
+        </is>
+      </c>
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
@@ -14732,72 +14724,94 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Supertone/supertonic</t>
+          <t>SamsungSDS-Research/SGuard-ContentFilter-2B-v1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>supertonic</t>
+          <t>SGuard-ContentFilter-2B-v1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>수퍼톤</t>
+          <t>삼성SDS 리서치</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://huggingface.co/Supertone/supertonic</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+          <t>https://huggingface.co/SamsungSDS-Research/SGuard-ContentFilter-2B-v1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2511.12497</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>실시간 대비 최대 167배 빠른 온디바이스 TTS로 66M 경량 파라미터라 서버 없이 엣지 배포에 적합</t>
+          <t>경량 2B로 안전성 평가 F1 0.83, Llama-Guard-4-12B(0.62)보다 우수해 저비용 콘텐츠 필터링에 적합</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Text, Audio</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>OpenRAIL</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K159" s="2" t="n">
-        <v>45979</v>
+        <v>45972</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>46001</v>
+        <v>45986</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="N159" s="3" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+        <v>2533560320</v>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>8192</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>BF16</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Onnx</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
+          <t>GraniteForCausalLM</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>ibm-granite/granite-3.3-2b-instruct</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Beavertails=83;HarmfulQA=92;OpenAI Moderation=74;ToxicChat=72;XSTest=94</t>
+        </is>
+      </c>
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
@@ -14805,33 +14819,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sionic-ai/comsat-embed-ja-0.3b-preview</t>
+          <t>datumo/E-star-12B-base</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>comsat-embed-ja-0.3b-preview</t>
+          <t>E-star-12B-base</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/comsat-embed-ja-0.3b-preview</t>
+          <t>https://huggingface.co/datumo/E-star-12B-base</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.3B 경량 모델로 JMTEB 11개 태스크에서 4B 이하 중 최고 NDCG@10, 저지연 검색에 적합</t>
+          <t>금융·법률 RAG 파이프라인 품질평가에 특화, 프런티어 모델 대비 저비용 자동평가 대안으로 적합</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>법률·전문서비스</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -14841,7 +14855,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>일본어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -14850,17 +14864,15 @@
         </is>
       </c>
       <c r="K160" s="2" t="n">
-        <v>46205</v>
+        <v>46105</v>
       </c>
       <c r="L160" s="2" t="n">
-        <v>46208</v>
+        <v>46164</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>314611968</v>
-      </c>
-      <c r="N160" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>11766034176</v>
+      </c>
+      <c r="N160" s="3" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>FP32</t>
@@ -14868,13 +14880,17 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>ModernBertModel</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr"/>
+          <t>Gemma3ForCausalLM</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>cl-nagoya/ruri-v3-310m</t>
+          <t>google/gemma-3-12b-it</t>
         </is>
       </c>
       <c r="S160" t="inlineStr"/>
@@ -14888,33 +14904,37 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sionic-ai/comsat-embed-ja-8b-preview</t>
+          <t>datumo/CAC-CoT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>comsat-embed-ja-8b-preview</t>
+          <t>CAC-CoT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/comsat-embed-ja-8b-preview</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>https://huggingface.co/datumo/CAC-CoT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.18743</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JMTEB(v2) 11개 태스크 평균 NDCG@10 0.8133로 비교 모델 중 최고, 일본어 검색에 적합</t>
+          <t>연결어 기반 압축 CoT로 해석 가능한 추론을 저지연으로 제공해 수학·논리 튜터링과 설명 가능한 QA에 적합</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>교육</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -14924,40 +14944,42 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>영어, 일본어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K161" s="2" t="n">
-        <v>46206</v>
+        <v>45793</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>46208</v>
+        <v>45915</v>
       </c>
       <c r="M161" s="3" t="n">
-        <v>7567295488</v>
-      </c>
-      <c r="N161" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>7070619136</v>
+      </c>
+      <c r="N161" s="3" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP32</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Qwen3Model</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr"/>
+          <t>Qwen2Model</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-Embedding-8B</t>
+          <t>Qwen/Qwen2.5-7B-Instruct</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
@@ -14971,28 +14993,28 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sionic-ai/comsat-embed-ko-8b-preview</t>
+          <t>saltlux/Ko-Llama3-Luxia-8B</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>comsat-embed-ko-8b-preview</t>
+          <t>Ko-Llama3-Luxia-8B</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>솔트룩스</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/comsat-embed-ko-8b-preview</t>
+          <t>https://huggingface.co/saltlux/Ko-Llama3-Luxia-8B</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MTEB 한국어 검색 9개 태스크 평균 NDCG@10 0.7930으로 비교 모델 중 최고, 한국어 검색에 적합</t>
+          <t>Llama-3-8B를 한국어 100GB 코퍼스로 추가 사전학습, 한국어 자연어 생성에 특화</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -15012,17 +15034,17 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>llama3</t>
         </is>
       </c>
       <c r="K162" s="2" t="n">
-        <v>46205</v>
+        <v>45412</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>46208</v>
+        <v>45419</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>7567295488</v>
+        <v>8173916160</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>8192</v>
@@ -15034,13 +15056,17 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Qwen3Model</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr"/>
+          <t>LlamaForCausalLM</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-Embedding-8B</t>
+          <t>Llama-3-8B</t>
         </is>
       </c>
       <c r="S162" t="inlineStr"/>
@@ -15054,76 +15080,68 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sionic-ai/bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
+          <t>Supertone/supertonic-3</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
+          <t>supertonic-3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>수퍼톤</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/bge-reasoner-embed-qwen3-8b-0923-AWQ-4bit</t>
+          <t>https://huggingface.co/Supertone/supertonic-3</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AWQ 4bit 양자화로 인코딩 속도 약 60% 향상, 검색 성능은 유지해 저지연 배포에 적합</t>
+          <t>31개 언어를 지원하는 99M 경량 온디바이스 TTS로 GPU 없이도 빠르게 동작해 로컬·엣지 배포에 적합</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>Text, Audio</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>다국어(31개 언어)</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>OpenRAIL</t>
         </is>
       </c>
       <c r="K163" s="2" t="n">
-        <v>45927</v>
+        <v>46148</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>45928</v>
+        <v>46160</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>8190735360</v>
+        <v>99000000</v>
       </c>
       <c r="N163" s="3" t="inlineStr"/>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>FP32+I32</t>
-        </is>
-      </c>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Qwen3ForCausalLM</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>BAAI/bge-reasoner-embed-qwen3-8b-0923</t>
-        </is>
-      </c>
+          <t>Onnx</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
@@ -15135,76 +15153,68 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sionic-ai/ko-gemma-2-9b-it-Q4_0-GGUF</t>
+          <t>Supertone/supertonic-2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ko-gemma-2-9b-it-Q4_0-GGUF</t>
+          <t>supertonic-2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>수퍼톤</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/ko-gemma-2-9b-it-Q4_0-GGUF</t>
+          <t>https://huggingface.co/Supertone/supertonic-2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>GGUF(Q4_0) 양자화로 llama.cpp에서 가볍게 구동되는 한국어 Gemma-2-9B 배포판</t>
+          <t>온디바이스 TTS로 실시간 대비 최대 167배 빠르고 66M 경량 파라미터라 엣지·모바일 배포에 적합</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Audio</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>다국어(5개 언어)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>OpenRAIL</t>
         </is>
       </c>
       <c r="K164" s="2" t="n">
-        <v>45517</v>
+        <v>46028</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>45517</v>
+        <v>46028</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>9000000000</v>
+        <v>66000000</v>
       </c>
       <c r="N164" s="3" t="inlineStr"/>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>GGUF(양자화)</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>rtzr/ko-gemma-2-9b-it</t>
-        </is>
-      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Onnx</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
@@ -15216,78 +15226,68 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sionic-ai/nllb-200-ko-gec-3.3B</t>
+          <t>Supertone/supertonic</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nllb-200-ko-gec-3.3B</t>
+          <t>supertonic</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>수퍼톤</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://huggingface.co/sionic-ai/nllb-200-ko-gec-3.3B</t>
+          <t>https://huggingface.co/Supertone/supertonic</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>facebook/nllb-200-3.3B를 파인튜닝한 한국어 문법 교정 특화 모델(한국어 그래멀리)</t>
+          <t>실시간 대비 최대 167배 빠른 온디바이스 TTS로 66M 경량 파라미터라 서버 없이 엣지 배포에 적합</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>교육</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Audio</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>다국어(196개 언어)</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>OpenRAIL</t>
         </is>
       </c>
       <c r="K165" s="2" t="n">
-        <v>45470</v>
+        <v>45979</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>45475</v>
+        <v>46001</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>3300000000</v>
-      </c>
-      <c r="N165" s="3" t="n">
-        <v>512</v>
-      </c>
+        <v>66000000</v>
+      </c>
+      <c r="N165" s="3" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>M2M100ForConditionalGeneration</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>facebook/nllb-200-3.3B</t>
-        </is>
-      </c>
+          <t>Onnx</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
@@ -15299,32 +15299,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
+          <t>yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
+          <t>YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>야놀자</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2403.07691</t>
+          <t>https://arxiv.org/abs/2507.13618</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LogicKor 6.62점으로 70B급 모델에 필적하는 Alpha-Instruct를 GPTQ 양자화해 경량 환경 추론에 적합</t>
+          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델로, 다국어 프로덕션 번역 파이프라인에 적합합니다.</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15339,42 +15339,44 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>기타(llama3)</t>
+          <t>openmdw-1.0</t>
         </is>
       </c>
       <c r="K166" s="2" t="n">
-        <v>45460</v>
+        <v>46064</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>45463</v>
+        <v>46064</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>8030261248</v>
-      </c>
-      <c r="N166" s="3" t="inlineStr"/>
+        <v>8304201728</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>8192</v>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>FP16+I32</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>MistralForCausalLM</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
+          <t>ByteDance-Seed/Seed-X-PPO-7B</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -15388,28 +15390,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
+          <t>yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Llama-3-Alpha-Ko-8B-Evo</t>
+          <t>YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>야놀자</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Evo</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2507.13618</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KoBEST·Haerae 기반 진화적 모델 병합으로 제작된 베이스 모델로, 다양한 태스크 파인튜닝의 출발점으로 적합</t>
+          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델로, 경량 배포 환경에 적합합니다.</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -15424,89 +15430,83 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>기타(llama3)</t>
+          <t>openmdw-1.0</t>
         </is>
       </c>
       <c r="K167" s="2" t="n">
-        <v>45435</v>
+        <v>46064</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>45436</v>
+        <v>46064</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>8030261248</v>
-      </c>
-      <c r="N167" s="3" t="inlineStr"/>
+        <v>8304627712</v>
+      </c>
+      <c r="N167" s="3" t="n">
+        <v>8192</v>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>F8_E4M3+FP32</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>MistralForCausalLM</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-8B, meta-llama/Meta-Llama-3-8B-Instruct, beomi/Llama-3-Open-Ko-8B</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>LogicKor_single=5.143;LogicKor_multi=5.238;KoBEST_boolq=85.47;KoBEST_copa=74.20;KoBEST_hellaswag=42.20;KoBEST_sentineg=94.71;KoBEST_wic=60.95</t>
-        </is>
-      </c>
+          <t>ByteDance-Seed/Seed-X-PPO-7B</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>LogicKor_single=5.143;LogicKor_multi=5.238;KoBEST_boolq=85.47;KoBEST_copa=74.20;KoBEST_hellaswag=42.20;KoBEST_sentineg=94.71;KoBEST_wic=60.95</t>
-        </is>
-      </c>
+      <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Llama-3-Alpha-Ko-8B-Instruct</t>
+          <t>YanoljaNEXT-Rosetta-12B-2510</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>야놀자</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2403.07691</t>
+          <t>https://arxiv.org/abs/2506.20920</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>LogicKor 6.62점으로 70B급 모델에 필적하는 성능을 달성해 복잡한 한국어 추론·대화 작업에 적합</t>
+          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -15521,22 +15521,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>기타(llama3)</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K168" s="2" t="n">
-        <v>45435</v>
+        <v>45939</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>45436</v>
+        <v>45963</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>8030261248</v>
+        <v>11766034176</v>
       </c>
       <c r="N168" s="3" t="inlineStr"/>
       <c r="O168" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>Gemma3ForCausalLM</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -15556,50 +15556,50 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>LogicKor_single=7.143;LogicKor_multi=6.065;KoBEST_boolq=83.69;KoBEST_copa=74.20;KoBEST_hellaswag=42.40;KoBEST_sentineg=92.44;KoBEST_wic=57.30</t>
-        </is>
-      </c>
+          <t>google/gemma-3-12b-pt</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>LogicKor_single=7.143;LogicKor_multi=6.065;KoBEST_boolq=83.69;KoBEST_copa=74.20;KoBEST_hellaswag=42.40;KoBEST_sentineg=92.44;KoBEST_wic=57.30</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr"/>
+      <c r="W168" t="inlineStr"/>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>CHrF++(WMT24++,En-Ko)=37.36</t>
+        </is>
+      </c>
       <c r="Y168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
+          <t>YanoljaNEXT-Rosetta-27B-2511</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>야놀자</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2506.20920</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>LogicKor 6.30점(4bit Marlin, Ampere GPU 최적화)으로 성능 손실 최소화한 고속 추론에 적합</t>
+          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15614,69 +15614,65 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>한국어</t>
+          <t>다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>기타(llama3)</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K169" s="2" t="n">
-        <v>45435</v>
+        <v>45963</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>45436</v>
+        <v>45963</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>8000000000</v>
+        <v>27009346304</v>
       </c>
       <c r="N169" s="3" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>INT4</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>Gemma3ForCausalLM</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>LogicKor_single=6.857;LogicKor_multi=5.738</t>
-        </is>
-      </c>
+          <t>google/gemma-3-27b-pt</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>LogicKor_single=6.857;LogicKor_multi=5.738</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr"/>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+        </is>
+      </c>
       <c r="Y169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511-FP8</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
+          <t>YanoljaNEXT-Rosetta-27B-2511-FP8</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -15686,17 +15682,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511-FP8</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2507.13618</t>
+          <t>https://arxiv.org/abs/2506.20920</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델로, 다국어 프로덕션 번역 파이프라인에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델로, 효율적 추론 배포에 적합합니다.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -15711,44 +15707,42 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>openmdw-1.0</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K170" s="2" t="n">
-        <v>46064</v>
+        <v>45963</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>46064</v>
+        <v>45963</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>8304201728</v>
-      </c>
-      <c r="N170" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>27010908704</v>
+      </c>
+      <c r="N170" s="3" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>BF16+F8_E4M3</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>MistralForCausalLM</t>
+          <t>Gemma3ForCausalLM</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>ByteDance-Seed/Seed-X-PPO-7B</t>
+          <t>google/gemma-3-27b-pt</t>
         </is>
       </c>
       <c r="S170" t="inlineStr"/>
@@ -15756,18 +15750,22 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+        </is>
+      </c>
       <c r="Y170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
+          <t>YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -15777,17 +15775,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Rosetta-7B-2602-FP8</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2507.13618</t>
+          <t>https://arxiv.org/abs/2506.20920</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델로, 경량 배포 환경에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공해 로컬 추론에 적합합니다.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -15802,36 +15800,30 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>openmdw-1.0</t>
+          <t>gemma</t>
         </is>
       </c>
       <c r="K171" s="2" t="n">
-        <v>46064</v>
+        <v>45963</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>46064</v>
+        <v>45963</v>
       </c>
       <c r="M171" s="3" t="n">
-        <v>8304627712</v>
-      </c>
-      <c r="N171" s="3" t="n">
-        <v>8192</v>
-      </c>
+        <v>27000000000</v>
+      </c>
+      <c r="N171" s="3" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
-          <t>F8_E4M3+FP32</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>MistralForCausalLM</t>
-        </is>
-      </c>
+          <t>GGUF(양자화)</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
           <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
@@ -15839,7 +15831,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>ByteDance-Seed/Seed-X-PPO-7B</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
         </is>
       </c>
       <c r="S171" t="inlineStr"/>
@@ -15847,18 +15839,22 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2510</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-12B-2510</t>
+          <t>YanoljaNEXT-Rosetta-4B-2510</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -15868,7 +15864,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2510</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15878,7 +15874,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델입니다.</t>
+          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -15902,13 +15898,13 @@
         </is>
       </c>
       <c r="K172" s="2" t="n">
-        <v>45939</v>
+        <v>45941</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>11766034176</v>
+        <v>3880263168</v>
       </c>
       <c r="N172" s="3" t="inlineStr"/>
       <c r="O172" t="inlineStr">
@@ -15928,7 +15924,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-pt</t>
+          <t>google/gemma-3-4b-pt</t>
         </is>
       </c>
       <c r="S172" t="inlineStr"/>
@@ -15938,7 +15934,7 @@
       <c r="W172" t="inlineStr"/>
       <c r="X172" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=37.36</t>
+          <t>CHrF++(WMT24++,En-Ko)=35.09</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr"/>
@@ -15946,12 +15942,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-27B-2511</t>
+          <t>YanoljaNEXT-Rosetta-4B-2511</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -15961,7 +15957,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15971,7 +15967,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델입니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -16001,7 +15997,7 @@
         <v>45963</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>27009346304</v>
+        <v>3880263168</v>
       </c>
       <c r="N173" s="3" t="inlineStr"/>
       <c r="O173" t="inlineStr">
@@ -16021,7 +16017,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>google/gemma-3-27b-pt</t>
+          <t>google/gemma-3-4b-pt</t>
         </is>
       </c>
       <c r="S173" t="inlineStr"/>
@@ -16031,7 +16027,7 @@
       <c r="W173" t="inlineStr"/>
       <c r="X173" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr"/>
@@ -16039,12 +16035,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511-FP8</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511-FP8</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-27B-2511-FP8</t>
+          <t>YanoljaNEXT-Rosetta-4B-2511-FP8</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -16054,7 +16050,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511-FP8</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511-FP8</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -16064,7 +16060,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델로, 효율적 추론 배포에 적합합니다.</t>
+          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적 번역 배포에 적합합니다.</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -16094,7 +16090,7 @@
         <v>45963</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>27010908704</v>
+        <v>3880459008</v>
       </c>
       <c r="N174" s="3" t="inlineStr"/>
       <c r="O174" t="inlineStr">
@@ -16114,7 +16110,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>google/gemma-3-27b-pt</t>
+          <t>google/gemma-3-4b-pt</t>
         </is>
       </c>
       <c r="S174" t="inlineStr"/>
@@ -16124,7 +16120,7 @@
       <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr"/>
@@ -16132,12 +16128,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
+          <t>YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -16147,7 +16143,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-27B-2511-GGUF</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -16157,7 +16153,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공해 로컬 추론에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합합니다.</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -16187,7 +16183,7 @@
         <v>45963</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>27000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="N175" s="3" t="inlineStr"/>
       <c r="O175" t="inlineStr">
@@ -16203,7 +16199,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-27B-2511</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
         </is>
       </c>
       <c r="S175" t="inlineStr"/>
@@ -16213,7 +16209,7 @@
       <c r="W175" t="inlineStr"/>
       <c r="X175" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=37.21</t>
+          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr"/>
@@ -16221,12 +16217,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2510</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B-2510</t>
+          <t>YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -16236,7 +16232,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2510</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -16246,7 +16242,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델입니다.</t>
+          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판입니다.</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -16270,33 +16266,29 @@
         </is>
       </c>
       <c r="K176" s="2" t="n">
-        <v>45941</v>
+        <v>45962</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>45963</v>
+        <v>45962</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>3880263168</v>
+        <v>12000000000</v>
       </c>
       <c r="N176" s="3" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
-          <t>BF16</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Gemma3ForCausalLM</t>
-        </is>
-      </c>
+          <t>GGUF(양자화)</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-pt</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
         </is>
       </c>
       <c r="S176" t="inlineStr"/>
@@ -16306,7 +16298,7 @@
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=35.09</t>
+          <t>CHrF++(WMT24++,En-Ko)=37.36</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr"/>
@@ -16314,12 +16306,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B-2511</t>
+          <t>YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -16329,7 +16321,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -16339,7 +16331,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델입니다.</t>
+          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -16363,33 +16355,29 @@
         </is>
       </c>
       <c r="K177" s="2" t="n">
-        <v>45963</v>
+        <v>45961</v>
       </c>
       <c r="L177" s="2" t="n">
-        <v>45963</v>
+        <v>45962</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>3880263168</v>
+        <v>4000000000</v>
       </c>
       <c r="N177" s="3" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
-          <t>BF16</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>Gemma3ForCausalLM</t>
-        </is>
-      </c>
+          <t>GGUF(양자화)</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-pt</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
         </is>
       </c>
       <c r="S177" t="inlineStr"/>
@@ -16399,7 +16387,7 @@
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
+          <t>CHrF++(WMT24++,En-Ko)=35.09</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr"/>
@@ -16407,12 +16395,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511-FP8</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-12B</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B-2511-FP8</t>
+          <t>YanoljaNEXT-Rosetta-12B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -16422,17 +16410,13 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511-FP8</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2506.20920</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적 번역 배포에 적합합니다.</t>
+          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델입니다.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16447,7 +16431,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -16456,18 +16440,18 @@
         </is>
       </c>
       <c r="K178" s="2" t="n">
-        <v>45963</v>
+        <v>45903</v>
       </c>
       <c r="L178" s="2" t="n">
-        <v>45963</v>
+        <v>45903</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>3880459008</v>
+        <v>11766034176</v>
       </c>
       <c r="N178" s="3" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
-          <t>BF16+F8_E4M3</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -16477,12 +16461,12 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-pt</t>
+          <t>google/gemma-3-12b-pt</t>
         </is>
       </c>
       <c r="S178" t="inlineStr"/>
@@ -16492,7 +16476,7 @@
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
+          <t>CHrF++(WMT24++,En-Ko)=34.75</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr"/>
@@ -16500,12 +16484,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-20B</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
+          <t>YanoljaNEXT-Rosetta-20B</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -16515,17 +16499,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2511-GGUF</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-20B</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.20920</t>
+          <t>https://arxiv.org/abs/2508.10925</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합합니다.</t>
+          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16540,38 +16524,42 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K179" s="2" t="n">
-        <v>45963</v>
+        <v>45902</v>
       </c>
       <c r="L179" s="2" t="n">
-        <v>45963</v>
+        <v>45903</v>
       </c>
       <c r="M179" s="3" t="n">
-        <v>4000000000</v>
+        <v>20914757184</v>
       </c>
       <c r="N179" s="3" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
-          <t>GGUF(양자화)</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr"/>
+          <t>BF16</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>GptOssForCausalLM</t>
+        </is>
+      </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2511</t>
+          <t>openai/gpt-oss-20b</t>
         </is>
       </c>
       <c r="S179" t="inlineStr"/>
@@ -16581,7 +16569,7 @@
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=35.64</t>
+          <t>CHrF++(WMT24++,En-Ko)=33.87</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr"/>
@@ -16589,12 +16577,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
+          <t>yanolja/YanoljaNEXT-Rosetta-4B</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
+          <t>YanoljaNEXT-Rosetta-4B</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -16604,17 +16592,13 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B-2510-GGUF</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2506.20920</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판입니다.</t>
+          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델입니다.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -16629,7 +16613,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -16638,29 +16622,33 @@
         </is>
       </c>
       <c r="K180" s="2" t="n">
-        <v>45962</v>
+        <v>45902</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>45962</v>
+        <v>45903</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>12000000000</v>
+        <v>3880263168</v>
       </c>
       <c r="N180" s="3" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>GGUF(양자화)</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr"/>
+          <t>BF16</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Gemma3ForCausalLM</t>
+        </is>
+      </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
+          <t>google/gemma-3-4b-pt</t>
         </is>
       </c>
       <c r="S180" t="inlineStr"/>
@@ -16670,7 +16658,7 @@
       <c r="W180" t="inlineStr"/>
       <c r="X180" t="inlineStr">
         <is>
-          <t>CHrF++(WMT24++,En-Ko)=37.36</t>
+          <t>CHrF++(WMT24++,En-Ko)=31.31</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr"/>
@@ -16678,12 +16666,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
+          <t>yanolja/YanoljaNEXT-EEVE-10.8B</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
+          <t>YanoljaNEXT-EEVE-10.8B</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -16693,17 +16681,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B-2510-GGUF</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-10.8B</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2506.20920</t>
+          <t>https://arxiv.org/abs/2402.14714</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델입니다.</t>
+          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -16718,38 +16706,42 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K181" s="2" t="n">
-        <v>45961</v>
+        <v>45329</v>
       </c>
       <c r="L181" s="2" t="n">
-        <v>45962</v>
+        <v>45898</v>
       </c>
       <c r="M181" s="3" t="n">
-        <v>4000000000</v>
+        <v>10804924416</v>
       </c>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
-          <t>GGUF(양자화)</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr"/>
+          <t>BF16</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>LlamaForCausalLM</t>
+        </is>
+      </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-12B-2510</t>
+          <t>upstage/SOLAR-10.7B-v1.0</t>
         </is>
       </c>
       <c r="S181" t="inlineStr"/>
@@ -16757,22 +16749,18 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" t="inlineStr"/>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>CHrF++(WMT24++,En-Ko)=35.09</t>
-        </is>
-      </c>
+      <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-12B</t>
+          <t>yanolja/YanoljaNEXT-EEVE-2.8B</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-12B</t>
+          <t>YanoljaNEXT-EEVE-2.8B</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -16782,13 +16770,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-12B</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-2.8B</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2402.14714</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델입니다.</t>
+          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -16803,22 +16795,22 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K182" s="2" t="n">
-        <v>45903</v>
+        <v>45344</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>45903</v>
+        <v>45898</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>11766034176</v>
+        <v>2819340864</v>
       </c>
       <c r="N182" s="3" t="inlineStr"/>
       <c r="O182" t="inlineStr">
@@ -16828,7 +16820,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gemma3ForCausalLM</t>
+          <t>PhiForCausalLM</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -16838,7 +16830,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-pt</t>
+          <t>microsoft/phi-2</t>
         </is>
       </c>
       <c r="S182" t="inlineStr"/>
@@ -16846,22 +16838,18 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" t="inlineStr"/>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>CHrF++(WMT24++,En-Ko)=34.75</t>
-        </is>
-      </c>
+      <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-20B</t>
+          <t>yanolja/YanoljaNEXT-EEVE-Instruct-10.8B</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-20B</t>
+          <t>YanoljaNEXT-EEVE-Instruct-10.8B</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -16871,17 +16859,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-20B</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-10.8B</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.10925</t>
+          <t>https://arxiv.org/abs/2402.14714</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델입니다.</t>
+          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델로, 한국어 대화 어시스턴트 용도에 적합합니다.</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -16896,7 +16884,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -16905,13 +16893,13 @@
         </is>
       </c>
       <c r="K183" s="2" t="n">
-        <v>45902</v>
+        <v>45344</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>45903</v>
+        <v>45898</v>
       </c>
       <c r="M183" s="3" t="n">
-        <v>20914757184</v>
+        <v>10804924416</v>
       </c>
       <c r="N183" s="3" t="inlineStr"/>
       <c r="O183" t="inlineStr">
@@ -16921,7 +16909,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>GptOssForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -16931,30 +16919,38 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
+          <t>yanolja/EEVE-Korean-10.8B-v1.0</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>AI2 Reasoning Challenge=64.85;HellaSwag=83.04;MMLU=64.23;Winogrande=81.93</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>GSM8K=50.72</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>TruthfulQA=54.09</t>
+        </is>
+      </c>
       <c r="W183" t="inlineStr"/>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>CHrF++(WMT24++,En-Ko)=33.87</t>
-        </is>
-      </c>
+      <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-Rosetta-4B</t>
+          <t>yanolja/YanoljaNEXT-EEVE-Instruct-2.8B</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-Rosetta-4B</t>
+          <t>YanoljaNEXT-EEVE-Instruct-2.8B</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -16964,13 +16960,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-Rosetta-4B</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-2.8B</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2402.14714</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델입니다.</t>
+          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델로, 경량 한국어 어시스턴트 용도에 적합합니다.</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -16985,22 +16985,22 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>gemma</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="K184" s="2" t="n">
-        <v>45902</v>
+        <v>45344</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>45903</v>
+        <v>45898</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>3880263168</v>
+        <v>2819340864</v>
       </c>
       <c r="N184" s="3" t="inlineStr"/>
       <c r="O184" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gemma3ForCausalLM</t>
+          <t>PhiForCausalLM</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -17020,30 +17020,38 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>google/gemma-3-4b-pt</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
+          <t>yanolja/EEVE-Korean-2.8B-v1.0</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>AI2 Reasoning Challenge=58.28;HellaSwag=72.42;MMLU=53.35;Winogrande=74.82</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>GSM8K=45.11</t>
+        </is>
+      </c>
       <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>TruthfulQA=48.32</t>
+        </is>
+      </c>
       <c r="W184" t="inlineStr"/>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>CHrF++(WMT24++,En-Ko)=31.31</t>
-        </is>
-      </c>
+      <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-10.8B</t>
+          <t>yanolja/YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-10.8B</t>
+          <t>YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -17053,17 +17061,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-10.8B</t>
+          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.14714</t>
+          <t>https://arxiv.org/abs/2310.01377</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델로, 해당 작업에 활용하기 적합합니다.</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -17087,13 +17095,13 @@
         </is>
       </c>
       <c r="K185" s="2" t="n">
-        <v>45329</v>
+        <v>45770</v>
       </c>
       <c r="L185" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>10804924416</v>
+        <v>7660481024</v>
       </c>
       <c r="N185" s="3" t="inlineStr"/>
       <c r="O185" t="inlineStr">
@@ -17103,7 +17111,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>Qwen2ForCausalLM</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -17113,7 +17121,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-10.7B-v1.0</t>
+          <t>yanolja/EEVE-Korean-7B-v2.0-Preview</t>
         </is>
       </c>
       <c r="S185" t="inlineStr"/>
@@ -17127,12 +17135,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-2.8B</t>
+          <t>yanolja/KoSOLAR-10.7B-v0.2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-2.8B</t>
+          <t>KoSOLAR-10.7B-v0.2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -17142,17 +17150,13 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-2.8B</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2402.14714</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/yanolja/KoSOLAR-10.7B-v0.2</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -17176,13 +17180,13 @@
         </is>
       </c>
       <c r="K186" s="2" t="n">
-        <v>45344</v>
+        <v>45309</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>45898</v>
+        <v>45322</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>2819340864</v>
+        <v>10804924416</v>
       </c>
       <c r="N186" s="3" t="inlineStr"/>
       <c r="O186" t="inlineStr">
@@ -17192,7 +17196,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>PhiForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -17202,7 +17206,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>microsoft/phi-2</t>
+          <t>upstage/SOLAR-10.7B-v1.0</t>
         </is>
       </c>
       <c r="S186" t="inlineStr"/>
@@ -17216,32 +17220,32 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-Instruct-10.8B</t>
+          <t>upstage/Solar-Open-100B</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-Instruct-10.8B</t>
+          <t>Solar-Open-100B</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>야놀자</t>
+          <t>업스테이지</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-10.8B</t>
+          <t>https://huggingface.co/upstage/Solar-Open-100B</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.14714</t>
+          <t>https://arxiv.org/abs/2601.07022</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델로, 한국어 대화 어시스턴트 용도에 적합합니다.</t>
+          <t>102B(활성 12B) MoE로 한국어 지식·의료 벤치마크서 경쟁 모델 상회, 기업용 에이전틱 활용에 적합</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -17261,88 +17265,82 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>기타(upstage-solar-license)</t>
         </is>
       </c>
       <c r="K187" s="2" t="n">
-        <v>45344</v>
+        <v>46001</v>
       </c>
       <c r="L187" s="2" t="n">
-        <v>45898</v>
+        <v>46052</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>10804924416</v>
-      </c>
-      <c r="N187" s="3" t="inlineStr"/>
+        <v>102651793408</v>
+      </c>
+      <c r="N187" s="3" t="n">
+        <v>131072</v>
+      </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>BF16+FP32</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>SolarOpenForCausalLM</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr">
-        <is>
-          <t>yanolja/EEVE-Korean-10.8B-v1.0</t>
-        </is>
-      </c>
+          <t>베이스 모델(프롬스크래치 사전학습)</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr">
         <is>
-          <t>AI2 Reasoning Challenge=64.85;HellaSwag=83.04;MMLU=64.23;Winogrande=81.93</t>
+          <t>KMMLU=73.0;KMMLU-Pro=64.0;CLIcK=78.9;HAE-RAE v1.1=73.3;KoBALT=44.3;KBankMMLU=65.5;KBL=65.5;KorMedMCQA=84.4;Ko-IFEval=87.5;Ko Arena Hard v2=79.9;MMLU=88.2;MMLU-Pro=80.4;GPQA-Diamond=68.1;HLE=10.5;IFBench=53.7;IFEval=88.0;Arena Hard v2=74.8;Writing Bench=7.51;AA-LCR=35.0</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>GSM8K=50.72</t>
+          <t>Ko-AIME 2024=80.3;Ko-AIME 2025=80.0;HRM8K=87.6;AIME 2024=91.7;AIME 2025=84.3;HMMT 2025 (Feb)=73.3;HMMT 2025 (Nov)=80.0;LiveCodeBench=74.2;Tau2 Airline=52.4;Tau2 Telecom=55.6;Tau2 Retail=59.3</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>TruthfulQA=54.09</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>KMMLU=73.0;KMMLU-Pro=64.0;CLIcK=78.9;HAE-RAE v1.1=73.3;KoBALT=44.3;KBankMMLU=65.5;KBL=65.5;KorMedMCQA=84.4;Ko-AIME 2024=80.3;Ko-AIME 2025=80.0;HRM8K=87.6;Ko-IFEval=87.5;Ko Arena Hard v2=79.9</t>
+        </is>
+      </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-Instruct-2.8B</t>
+          <t>upstage/solar-pro-preview-instruct</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-Instruct-2.8B</t>
+          <t>solar-pro-preview-instruct</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>야놀자</t>
+          <t>업스테이지</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-2.8B</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2402.14714</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/upstage/solar-pro-preview-instruct</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델로, 경량 한국어 어시스턴트 용도에 적합합니다.</t>
+          <t>단일 GPU에 탑재되는 22B로 70B급 Llama-3.1과 동등 성능, 온프레미스 배포에 적합</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -17357,24 +17355,26 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="K188" s="2" t="n">
-        <v>45344</v>
+        <v>45544</v>
       </c>
       <c r="L188" s="2" t="n">
-        <v>45898</v>
+        <v>45555</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>2819340864</v>
-      </c>
-      <c r="N188" s="3" t="inlineStr"/>
+        <v>22140032000</v>
+      </c>
+      <c r="N188" s="3" t="n">
+        <v>4096</v>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>BF16</t>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>PhiForCausalLM</t>
+          <t>SolarForCausalLM</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -17392,25 +17392,21 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>yanolja/EEVE-Korean-2.8B-v1.0</t>
+          <t>Phi-3-medium</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>AI2 Reasoning Challenge=58.28;HellaSwag=72.42;MMLU=53.35;Winogrande=74.82</t>
+          <t>MMLU=79.14;MMLU Pro=52.11;IFEval=84.37;ARC-C=68.86;GPQA=36.38;HellaSwag=86.36;EQBench=77.91;BigBench Hard=67.31;MUSR=45.85</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>GSM8K=45.11</t>
+          <t>GSM8K=89.69;MBPP=61.59</t>
         </is>
       </c>
       <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>TruthfulQA=48.32</t>
-        </is>
-      </c>
+      <c r="V188" t="inlineStr"/>
       <c r="W188" t="inlineStr"/>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr"/>
@@ -17418,32 +17414,32 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>yanolja/YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
+          <t>upstage/SOLAR-10.7B-Instruct-v1.0</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
+          <t>SOLAR-10.7B-Instruct-v1.0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>야놀자</t>
+          <t>업스테이지</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/YanoljaNEXT-EEVE-Instruct-7B-v2-Preview</t>
+          <t>https://huggingface.co/upstage/SOLAR-10.7B-Instruct-v1.0</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.01377</t>
+          <t>https://arxiv.org/abs/2312.15166</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델로, 해당 작업에 활용하기 적합합니다.</t>
+          <t>H6 평균 74.20로 46.7B Mixtral-8x7B보다 우수한 11B급 성능, 단일턴 대화에 최적화</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -17458,32 +17454,32 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K189" s="2" t="n">
-        <v>45770</v>
+        <v>45272</v>
       </c>
       <c r="L189" s="2" t="n">
-        <v>45898</v>
+        <v>45545</v>
       </c>
       <c r="M189" s="3" t="n">
-        <v>7660481024</v>
+        <v>10731524096</v>
       </c>
       <c r="N189" s="3" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Qwen2ForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -17493,7 +17489,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>yanolja/EEVE-Korean-7B-v2.0-Preview</t>
+          <t>upstage/SOLAR-10.7B-v1.0</t>
         </is>
       </c>
       <c r="S189" t="inlineStr"/>
@@ -17507,28 +17503,32 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>yanolja/KoSOLAR-10.7B-v0.2</t>
+          <t>upstage/SOLAR-10.7B-v1.0</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>KoSOLAR-10.7B-v0.2</t>
+          <t>SOLAR-10.7B-v1.0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>야놀자</t>
+          <t>업스테이지</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://huggingface.co/yanolja/KoSOLAR-10.7B-v0.2</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
+          <t>https://huggingface.co/upstage/SOLAR-10.7B-v1.0</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2312.15166</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>Depth Up-Scaling으로 만든 30B 미만 최고 성능 사전학습 베이스, 파인튜닝 기반으로 이상적</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -17552,18 +17552,18 @@
         </is>
       </c>
       <c r="K190" s="2" t="n">
-        <v>45309</v>
+        <v>45272</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>45322</v>
+        <v>45545</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>10804924416</v>
+        <v>10731524096</v>
       </c>
       <c r="N190" s="3" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -17573,12 +17573,12 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>베이스 모델(프롬스크래치 사전학습)</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-10.7B-v1.0</t>
+          <t>Mistral 7B</t>
         </is>
       </c>
       <c r="S190" t="inlineStr"/>
@@ -17592,12 +17592,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>upstage/Solar-Open-100B</t>
+          <t>upstage/SOLAR-0-70b-16bit</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Solar-Open-100B</t>
+          <t>SOLAR-0-70b-16bit</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -17607,17 +17607,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/Solar-Open-100B</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2601.07022</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/upstage/SOLAR-0-70b-16bit</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>102B(활성 12B) MoE로 한국어 지식·의료 벤치마크서 경쟁 모델 상회, 기업용 에이전틱 활용에 적합</t>
+          <t>출시 당시 Open LLM 리더보드 70B 모델 중 세계 1위 기록(H4 73), Orca+Alpaca SFT로 지시응답에 적합</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -17632,71 +17628,69 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>기타(upstage-solar-license)</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K191" s="2" t="n">
-        <v>46001</v>
+        <v>45137</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>46052</v>
+        <v>45182</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>102651793408</v>
-      </c>
-      <c r="N191" s="3" t="n">
-        <v>131072</v>
-      </c>
+        <v>70000000000</v>
+      </c>
+      <c r="N191" s="3" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>BF16+FP32</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>SolarOpenForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr"/>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>LLaMA-2</t>
+        </is>
+      </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>KMMLU=73.0;KMMLU-Pro=64.0;CLIcK=78.9;HAE-RAE v1.1=73.3;KoBALT=44.3;KBankMMLU=65.5;KBL=65.5;KorMedMCQA=84.4;Ko-IFEval=87.5;Ko Arena Hard v2=79.9;MMLU=88.2;MMLU-Pro=80.4;GPQA-Diamond=68.1;HLE=10.5;IFBench=53.7;IFEval=88.0;Arena Hard v2=74.8;Writing Bench=7.51;AA-LCR=35.0</t>
-        </is>
-      </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>Ko-AIME 2024=80.3;Ko-AIME 2025=80.0;HRM8K=87.6;AIME 2024=91.7;AIME 2025=84.3;HMMT 2025 (Feb)=73.3;HMMT 2025 (Nov)=80.0;LiveCodeBench=74.2;Tau2 Airline=52.4;Tau2 Telecom=55.6;Tau2 Retail=59.3</t>
-        </is>
-      </c>
+          <t>ARC=71.1;HellaSwag=87.9;MMLU=70.6;MT-Bench=7.44063</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>KMMLU=73.0;KMMLU-Pro=64.0;CLIcK=78.9;HAE-RAE v1.1=73.3;KoBALT=44.3;KBankMMLU=65.5;KBL=65.5;KorMedMCQA=84.4;Ko-AIME 2024=80.3;Ko-AIME 2025=80.0;HRM8K=87.6;Ko-IFEval=87.5;Ko Arena Hard v2=79.9</t>
-        </is>
-      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>TruthfulQA=62.2</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr"/>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>upstage/solar-pro-preview-instruct</t>
+          <t>upstage/SOLAR-0-70b-8bit</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>solar-pro-preview-instruct</t>
+          <t>SOLAR-0-70b-8bit</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -17706,13 +17700,13 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/solar-pro-preview-instruct</t>
+          <t>https://huggingface.co/upstage/SOLAR-0-70b-8bit</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>단일 GPU에 탑재되는 22B로 70B급 Llama-3.1과 동등 성능, 온프레미스 배포에 적합</t>
+          <t>리더보드 1위였던 SOLAR-0-70b-16bit의 8bit 양자화 버전, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -17732,51 +17726,41 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K192" s="2" t="n">
-        <v>45544</v>
+        <v>45154</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>45555</v>
+        <v>45166</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>22140032000</v>
-      </c>
-      <c r="N192" s="3" t="n">
-        <v>4096</v>
-      </c>
+        <v>70000000000</v>
+      </c>
+      <c r="N192" s="3" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>INT8</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>SolarForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Phi-3-medium</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>MMLU=79.14;MMLU Pro=52.11;IFEval=84.37;ARC-C=68.86;GPQA=36.38;HellaSwag=86.36;EQBench=77.91;BigBench Hard=67.31;MUSR=45.85</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>GSM8K=89.69;MBPP=61.59</t>
-        </is>
-      </c>
+          <t>LLaMA-2, upstage/SOLAR-0-70b-16bit</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" t="inlineStr"/>
@@ -17786,12 +17770,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-10.7B-Instruct-v1.0</t>
+          <t>upstage/Llama-2-70b-instruct</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SOLAR-10.7B-Instruct-v1.0</t>
+          <t>Llama-2-70b-instruct</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -17801,17 +17785,13 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/SOLAR-10.7B-Instruct-v1.0</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2312.15166</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/upstage/Llama-2-70b-instruct</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>H6 평균 74.20로 46.7B Mixtral-8x7B보다 우수한 11B급 성능, 단일턴 대화에 최적화</t>
+          <t>출시 당시 Open LLM 리더보드 70B 모델 중 세계 1위 기록, Orca 스타일 SFT로 지시응답에 적합</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -17835,20 +17815,16 @@
         </is>
       </c>
       <c r="K193" s="2" t="n">
-        <v>45272</v>
+        <v>45131</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>45545</v>
+        <v>45141</v>
       </c>
       <c r="M193" s="3" t="n">
-        <v>10731524096</v>
+        <v>70000000000</v>
       </c>
       <c r="N193" s="3" t="inlineStr"/>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>FP16</t>
-        </is>
-      </c>
+      <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>LlamaForCausalLM</t>
@@ -17861,13 +17837,21 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-10.7B-v1.0</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr"/>
+          <t>LLaMA-2</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>ARC=70.9;HellaSwag=87.5;MMLU=69.8;MT-Bench=7.24375</t>
+        </is>
+      </c>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>TruthfulQA=61</t>
+        </is>
+      </c>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr"/>
@@ -17875,42 +17859,42 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-10.7B-v1.0</t>
+          <t>NCSOFT/GME-VARCO-VISION-Embedding</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SOLAR-10.7B-v1.0</t>
+          <t>GME-VARCO-VISION-Embedding</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>업스테이지</t>
+          <t>엔씨소프트</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/SOLAR-10.7B-v1.0</t>
+          <t>https://huggingface.co/NCSOFT/GME-VARCO-VISION-Embedding</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2312.15166</t>
+          <t>https://arxiv.org/abs/2512.16925</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Depth Up-Scaling으로 만든 30B 미만 최고 성능 사전학습 베이스, 파인튜닝 기반으로 이상적</t>
+          <t>MultiVENT2.0에서 SOTA 제로샷 성능을 달성해 영상 검색·질의응답 기반 멀티모달 리트리벌에 적합</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>산업 전반·범용</t>
+          <t>콘텐츠·미디어·엔터테인먼트</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image, Video</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -17920,37 +17904,37 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="K194" s="2" t="n">
-        <v>45272</v>
+        <v>45818</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>45545</v>
+        <v>46030</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>10731524096</v>
+        <v>8291375616</v>
       </c>
       <c r="N194" s="3" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>BF16+FP32</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>Qwen2VLForConditionalGeneration</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Mistral 7B</t>
+          <t>Qwen/Qwen2-VL-7B-Instruct</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
@@ -17964,28 +17948,32 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-0-70b-16bit</t>
+          <t>NCSOFT/VARCO-VISION-2.0-1.7B</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SOLAR-0-70b-16bit</t>
+          <t>VARCO-VISION-2.0-1.7B</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>업스테이지</t>
+          <t>엔씨소프트</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/SOLAR-0-70b-16bit</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
+          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-1.7B</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.10105</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>출시 당시 Open LLM 리더보드 70B 모델 중 세계 1위 기록(H4 73), Orca+Alpaca SFT로 지시응답에 적합</t>
+          <t>1.7B 경량 모델로 온디바이스 구동 가능, 한국어 벤치마크 평균 65.4로 동급 최고 성능</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -17995,12 +17983,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -18009,13 +17997,13 @@
         </is>
       </c>
       <c r="K195" s="2" t="n">
-        <v>45137</v>
+        <v>45846</v>
       </c>
       <c r="L195" s="2" t="n">
-        <v>45182</v>
+        <v>45915</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>70000000000</v>
+        <v>2124391328</v>
       </c>
       <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" t="inlineStr">
@@ -18025,7 +18013,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>LlavaOnevisionForConditionalGeneration</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -18035,50 +18023,58 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>LLaMA-2</t>
+          <t>Qwen/Qwen3-1.7B, google/siglip2-so400m-patch16-384</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>ARC=71.1;HellaSwag=87.9;MMLU=70.6;MT-Bench=7.44063</t>
+          <t>MMLU=55.3;MT-Bench=72.3;KMMLU=10.4;KoMT-Bench=59.1;LogicKor=53.7</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>TruthfulQA=62.2</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>K-MMBench_DEV=77.9;K-MMStar=40.8;K-SEED=70.7;K-LLaVA-W=73.5;K-DTCBench=64.2;MMStar=54.5;MMMU_VAL=44.1;MathVista=61.1;OCRBench=83.0;AI2D=76.0;HallusionBench=43.0;MMVet=52.7;SEEDBench_IMG=74.5;LLaVABench=77.3;RealWorldQA=66.8;POPE=88.6;ScienceQA_TEST=84.0;SEEDBench2_Plus=66.9;BLINK=47.2;TextVQA_VAL=77.0;ChartQA_TEST=75.7;Q-Bench1_VAL=72.3;A-Bench_VAL=72.4;DocVQA_TEST=83.5;InfoVQA_TEST=65.0;K-Viscuit=57.7;PangeaBench(ko)=63.8;CORD=96.2;ICDAR2013=95.9;ICDAR2015=73.7</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>K-MMBench_DEV=77.9;K-MMStar=40.8;K-SEED=70.7;K-LLaVA-W=73.5;K-DTCBench=64.2;KMMLU=10.4;KoMT-Bench=59.1;LogicKor=53.7;K-Viscuit=57.7;PangeaBench(ko)=63.8</t>
+        </is>
+      </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>upstage/SOLAR-0-70b-8bit</t>
+          <t>NCSOFT/VARCO-VISION-2.0-1.7B-OCR</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SOLAR-0-70b-8bit</t>
+          <t>VARCO-VISION-2.0-1.7B-OCR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>업스테이지</t>
+          <t>엔씨소프트</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/SOLAR-0-70b-8bit</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
+          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-1.7B-OCR</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.10105</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>리더보드 1위였던 SOLAR-0-70b-16bit의 8bit 양자화 버전, 경량 배포에 적합</t>
+          <t>경량 OCR 특화 모델, CORD(95.6)·ICDAR2013(95.5)에서 상용 OCR 능가해 실시간 인식에 적합</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -18088,12 +18084,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -18102,38 +18098,42 @@
         </is>
       </c>
       <c r="K196" s="2" t="n">
-        <v>45154</v>
+        <v>45846</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>45166</v>
+        <v>45915</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>70000000000</v>
+        <v>2124391328</v>
       </c>
       <c r="N196" s="3" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
-          <t>INT8</t>
+          <t>FP16</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>LlavaOnevisionForConditionalGeneration</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>LLaMA-2, upstage/SOLAR-0-70b-16bit</t>
+          <t>Qwen/Qwen3-1.7B, google/siglip2-so400m-patch16-384</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>CORD=95.6;ICDAR2013=95.5;ICDAR2015=75.4</t>
+        </is>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" t="inlineStr"/>
       <c r="X196" t="inlineStr"/>
@@ -18142,28 +18142,32 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>upstage/Llama-2-70b-instruct</t>
+          <t>NCSOFT/VARCO-VISION-2.0-14B</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Llama-2-70b-instruct</t>
+          <t>VARCO-VISION-2.0-14B</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>업스테이지</t>
+          <t>엔씨소프트</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://huggingface.co/upstage/Llama-2-70b-instruct</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-14B</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.10105</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>출시 당시 Open LLM 리더보드 70B 모델 중 세계 1위 기록, Orca 스타일 SFT로 지시응답에 적합</t>
+          <t>한국어 벤치마크 평균 80.7로 최고 성능, 멀티이미지·문서 이해에 강한 한영 VLM</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -18173,12 +18177,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Text, Image</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -18187,19 +18191,23 @@
         </is>
       </c>
       <c r="K197" s="2" t="n">
-        <v>45131</v>
+        <v>45846</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>45141</v>
+        <v>45915</v>
       </c>
       <c r="M197" s="3" t="n">
-        <v>70000000000</v>
+        <v>15195602848</v>
       </c>
       <c r="N197" s="3" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>FP16</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>LlamaForCausalLM</t>
+          <t>LlavaOnevisionForConditionalGeneration</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -18209,34 +18217,38 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>LLaMA-2</t>
+          <t>Qwen/Qwen3-14B, google/siglip2-so400m-patch16-384</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>ARC=70.9;HellaSwag=87.5;MMLU=69.8;MT-Bench=7.24375</t>
+          <t>MMLU=77.9;MT-Bench=89.8;KMMLU=57.5;KoMT-Bench=78.3;LogicKor=74.0</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>TruthfulQA=61</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr"/>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>K-MMBench_DEV=87.7;K-MMStar=63.6;K-SEED=77.2;K-LLaVA-W=96.5;K-DTCBench=78.3;MMStar=66.9;MMMU_VAL=61.9;MathVista=73.2;OCRBench=86.9;AI2D=85.7;HallusionBench=53.2;MMVet=68.9;SEEDBench_IMG=78.0;LLaVABench=90.2;RealWorldQA=74.6;POPE=89.2;ScienceQA_TEST=93.5;SEEDBench2_Plus=71.9;BLINK=54.5;TextVQA_VAL=80.4;ChartQA_TEST=84.2;Q-Bench1_VAL=79.9;A-Bench_VAL=79.5;DocVQA_TEST=90.9;InfoVQA_TEST=80.4;K-Viscuit=73.7;PangeaBench(ko)=74.5;CORD=97.1;ICDAR2013=95.7;ICDAR2015=79.4</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>K-MMBench_DEV=87.7;K-MMStar=63.6;K-SEED=77.2;K-LLaVA-W=96.5;K-DTCBench=78.3;KMMLU=57.5;KoMT-Bench=78.3;LogicKor=74.0;K-Viscuit=73.7;PangeaBench(ko)=74.5</t>
+        </is>
+      </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>NCSOFT/GME-VARCO-VISION-Embedding</t>
+          <t>NCSOFT/VARCO-VISION-14B</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GME-VARCO-VISION-Embedding</t>
+          <t>VARCO-VISION-14B</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -18246,32 +18258,32 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/GME-VARCO-VISION-Embedding</t>
+          <t>https://huggingface.co/NCSOFT/VARCO-VISION-14B</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2512.16925</t>
+          <t>https://arxiv.org/abs/2411.19103</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MultiVENT2.0에서 SOTA 제로샷 성능을 달성해 영상 검색·질의응답 기반 멀티모달 리트리벌에 적합</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>콘텐츠·미디어·엔터테인먼트</t>
+          <t>산업 전반·범용</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Text, Image, Video</t>
+          <t>Text, Image</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어, 영어</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -18280,23 +18292,23 @@
         </is>
       </c>
       <c r="K198" s="2" t="n">
-        <v>45818</v>
+        <v>45621</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>46030</v>
+        <v>45912</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>8291375616</v>
+        <v>15195926048</v>
       </c>
       <c r="N198" s="3" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
-          <t>BF16+FP32</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Qwen2VLForConditionalGeneration</t>
+          <t>LlavaQwenForCausalLM</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -18306,7 +18318,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Qwen/Qwen2-VL-7B-Instruct</t>
+          <t>Qwen/Qwen2.5-14B-Instruct, google/siglip-so400m-patch14-384</t>
         </is>
       </c>
       <c r="S198" t="inlineStr"/>
@@ -18320,12 +18332,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NCSOFT/VARCO-VISION-2.0-1.7B</t>
+          <t>NCSOFT/VARCO-VISION-14B-HF</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>VARCO-VISION-2.0-1.7B</t>
+          <t>VARCO-VISION-14B-HF</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -18335,17 +18347,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-1.7B</t>
+          <t>https://huggingface.co/NCSOFT/VARCO-VISION-14B-HF</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.10105</t>
+          <t>https://arxiv.org/abs/2411.19103</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>1.7B 경량 모델로 온디바이스 구동 가능, 한국어 벤치마크 평균 65.4로 동급 최고 성능</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -18369,13 +18381,13 @@
         </is>
       </c>
       <c r="K199" s="2" t="n">
-        <v>45846</v>
+        <v>45623</v>
       </c>
       <c r="L199" s="2" t="n">
-        <v>45915</v>
+        <v>45912</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>2124391328</v>
+        <v>15195977248</v>
       </c>
       <c r="N199" s="3" t="inlineStr"/>
       <c r="O199" t="inlineStr">
@@ -18395,38 +18407,26 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-1.7B, google/siglip2-so400m-patch16-384</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>MMLU=55.3;MT-Bench=72.3;KMMLU=10.4;KoMT-Bench=59.1;LogicKor=53.7</t>
-        </is>
-      </c>
+          <t>Qwen/Qwen2.5-14B-Instruct, google/siglip-so400m-patch14-384</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>K-MMBench_DEV=77.9;K-MMStar=40.8;K-SEED=70.7;K-LLaVA-W=73.5;K-DTCBench=64.2;MMStar=54.5;MMMU_VAL=44.1;MathVista=61.1;OCRBench=83.0;AI2D=76.0;HallusionBench=43.0;MMVet=52.7;SEEDBench_IMG=74.5;LLaVABench=77.3;RealWorldQA=66.8;POPE=88.6;ScienceQA_TEST=84.0;SEEDBench2_Plus=66.9;BLINK=47.2;TextVQA_VAL=77.0;ChartQA_TEST=75.7;Q-Bench1_VAL=72.3;A-Bench_VAL=72.4;DocVQA_TEST=83.5;InfoVQA_TEST=65.0;K-Viscuit=57.7;PangeaBench(ko)=63.8;CORD=96.2;ICDAR2013=95.9;ICDAR2015=73.7</t>
-        </is>
-      </c>
+      <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>K-MMBench_DEV=77.9;K-MMStar=40.8;K-SEED=70.7;K-LLaVA-W=73.5;K-DTCBench=64.2;KMMLU=10.4;KoMT-Bench=59.1;LogicKor=53.7;K-Viscuit=57.7;PangeaBench(ko)=63.8</t>
-        </is>
-      </c>
+      <c r="W199" t="inlineStr"/>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NCSOFT/VARCO-VISION-2.0-1.7B-OCR</t>
+          <t>NCSOFT/Llama-VARCO-8B-Instruct</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VARCO-VISION-2.0-1.7B-OCR</t>
+          <t>Llama-VARCO-8B-Instruct</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -18436,17 +18436,13 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-1.7B-OCR</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2509.10105</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/NCSOFT/Llama-VARCO-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>경량 OCR 특화 모델, CORD(95.6)·ICDAR2013(95.5)에서 상용 OCR 능가해 실시간 인식에 적합</t>
+          <t>LogicKor 8.82점으로 동급 모델 중 최고 수준인 한국어 특화 챗봇에 적합</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -18456,7 +18452,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Text, Image</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -18466,27 +18462,27 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>llama3.1</t>
         </is>
       </c>
       <c r="K200" s="2" t="n">
-        <v>45846</v>
+        <v>45547</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>45915</v>
+        <v>45636</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>2124391328</v>
+        <v>8030261248</v>
       </c>
       <c r="N200" s="3" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>LlavaOnevisionForConditionalGeneration</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -18496,30 +18492,34 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-1.7B, google/siglip2-so400m-patch16-384</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr"/>
+          <t>meta-llama/Meta-Llama-3.1-8B</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>LogicKor Single turn=8.69;LogicKor Multi turn=8.95</t>
+        </is>
+      </c>
       <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>CORD=95.6;ICDAR2013=95.5;ICDAR2015=75.4</t>
-        </is>
-      </c>
+      <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>LogicKor Single turn=8.69;LogicKor Multi turn=8.95</t>
+        </is>
+      </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>NCSOFT/VARCO-VISION-2.0-14B</t>
+          <t>NCSOFT/Llama-3-OffsetBias-RM-8B</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>VARCO-VISION-2.0-14B</t>
+          <t>Llama-3-OffsetBias-RM-8B</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -18529,17 +18529,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/VARCO-VISION-2.0-14B</t>
+          <t>https://huggingface.co/NCSOFT/Llama-3-OffsetBias-RM-8B</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2509.10105</t>
+          <t>https://arxiv.org/abs/2407.06551</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>한국어 벤치마크 평균 80.7로 최고 성능, 멀티이미지·문서 이해에 강한 한영 VLM</t>
+          <t>RewardBench Chat 97.21점의 고성능 리워드 모델로 RLHF 보상 신호 산출에 적합</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -18549,78 +18549,74 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Text, Image</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>llama3</t>
         </is>
       </c>
       <c r="K201" s="2" t="n">
-        <v>45846</v>
+        <v>45484</v>
       </c>
       <c r="L201" s="2" t="n">
-        <v>45915</v>
+        <v>45541</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>15195602848</v>
+        <v>7504928768</v>
       </c>
       <c r="N201" s="3" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>BF16</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>LlavaOnevisionForConditionalGeneration</t>
+          <t>LlamaForSequenceClassification</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>병합 모델(mergekit 등)</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-14B, google/siglip2-so400m-patch16-384</t>
+          <t>sfairXC/FsfairX-LLaMA3-RM-v0.1, meta-llama/Meta-Llama-3-8B-Instruct</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>MMLU=77.9;MT-Bench=89.8;KMMLU=57.5;KoMT-Bench=78.3;LogicKor=74.0</t>
+          <t>RewardBench Chat=97.21;RewardBench Chat Hard=80.70;RewardBench Reasoning=90.60</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>K-MMBench_DEV=87.7;K-MMStar=63.6;K-SEED=77.2;K-LLaVA-W=96.5;K-DTCBench=78.3;MMStar=66.9;MMMU_VAL=61.9;MathVista=73.2;OCRBench=86.9;AI2D=85.7;HallusionBench=53.2;MMVet=68.9;SEEDBench_IMG=78.0;LLaVABench=90.2;RealWorldQA=74.6;POPE=89.2;ScienceQA_TEST=93.5;SEEDBench2_Plus=71.9;BLINK=54.5;TextVQA_VAL=80.4;ChartQA_TEST=84.2;Q-Bench1_VAL=79.9;A-Bench_VAL=79.5;DocVQA_TEST=90.9;InfoVQA_TEST=80.4;K-Viscuit=73.7;PangeaBench(ko)=74.5;CORD=97.1;ICDAR2013=95.7;ICDAR2015=79.4</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>K-MMBench_DEV=87.7;K-MMStar=63.6;K-SEED=77.2;K-LLaVA-W=96.5;K-DTCBench=78.3;KMMLU=57.5;KoMT-Bench=78.3;LogicKor=74.0;K-Viscuit=73.7;PangeaBench(ko)=74.5</t>
-        </is>
-      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>RewardBench Safety=89.01;EvalBiasBench Length=82.4;EvalBiasBench Concreteness=92.9;EvalBiasBench Empty Reference=46.2;EvalBiasBench Content Continuation=100.0;EvalBiasBench Nested Instruction=83.3;EvalBiasBench Familiar Knowledge=58.3</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr"/>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NCSOFT/VARCO-VISION-14B</t>
+          <t>NCSOFT/Llama-3-OffsetBias-8B</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>VARCO-VISION-14B</t>
+          <t>Llama-3-OffsetBias-8B</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -18630,17 +18626,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/VARCO-VISION-14B</t>
+          <t>https://huggingface.co/NCSOFT/Llama-3-OffsetBias-8B</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.19103</t>
+          <t>https://arxiv.org/abs/2407.06551</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>평가 편향에 강건하도록 학습된 LLM 심사 모델로 페어와이즈 응답 평가에 적합</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -18650,27 +18646,27 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Text, Image</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>llama3</t>
         </is>
       </c>
       <c r="K202" s="2" t="n">
-        <v>45621</v>
+        <v>45484</v>
       </c>
       <c r="L202" s="2" t="n">
-        <v>45912</v>
+        <v>45496</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>15195926048</v>
+        <v>8030261248</v>
       </c>
       <c r="N202" s="3" t="inlineStr"/>
       <c r="O202" t="inlineStr">
@@ -18680,7 +18676,7 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>LlavaQwenForCausalLM</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -18690,13 +18686,21 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Qwen/Qwen2.5-14B-Instruct, google/siglip-so400m-patch14-384</t>
-        </is>
-      </c>
-      <c r="S202" t="inlineStr"/>
+          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>LLMBar Natural=86.5;LLMBar Neighbor=81.0;LLMBar GPTInst=91.8;LLMBar GPTOut=60.6;LLMBar Manual=71.7</t>
+        </is>
+      </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>EvalBiasBench Length=85.3;EvalBiasBench Concreteness=100.0;EvalBiasBench Empty Reference=92.3;EvalBiasBench Content Continuation=95.8;EvalBiasBench Nested Instruction=50.0;EvalBiasBench Familiar Knowledge=83.3</t>
+        </is>
+      </c>
       <c r="W202" t="inlineStr"/>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr"/>
@@ -18704,32 +18708,32 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NCSOFT/VARCO-VISION-14B-HF</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>VARCO-VISION-14B-HF</t>
+          <t>Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/VARCO-VISION-14B-HF</t>
+          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct-GPTQ</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2411.19103</t>
+          <t>https://arxiv.org/abs/2403.07691</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>LogicKor 6.62점으로 70B급 모델에 필적하는 Alpha-Instruct를 GPTQ 양자화해 경량 환경 추론에 적합</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -18739,47 +18743,47 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Text, Image</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>기타(llama3)</t>
         </is>
       </c>
       <c r="K203" s="2" t="n">
-        <v>45623</v>
+        <v>45460</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>45912</v>
+        <v>45463</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>15195977248</v>
+        <v>8030261248</v>
       </c>
       <c r="N203" s="3" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
-          <t>FP16</t>
+          <t>FP16+I32</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>LlavaOnevisionForConditionalGeneration</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Qwen/Qwen2.5-14B-Instruct, google/siglip-so400m-patch14-384</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="S203" t="inlineStr"/>
@@ -18793,28 +18797,28 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NCSOFT/Llama-VARCO-8B-Instruct</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Llama-VARCO-8B-Instruct</t>
+          <t>Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/Llama-VARCO-8B-Instruct</t>
+          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>LogicKor 8.82점으로 동급 모델 중 최고 수준인 한국어 특화 챗봇에 적합</t>
+          <t>KoBEST·Haerae 기반 진화적 모델 병합으로 제작된 베이스 모델로, 다양한 태스크 파인튜닝의 출발점으로 적합</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -18829,19 +18833,19 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>한국어, 영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>llama3.1</t>
+          <t>기타(llama3)</t>
         </is>
       </c>
       <c r="K204" s="2" t="n">
-        <v>45547</v>
+        <v>45435</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>45636</v>
+        <v>45436</v>
       </c>
       <c r="M204" s="3" t="n">
         <v>8030261248</v>
@@ -18859,17 +18863,17 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>병합 모델(mergekit 등)</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3.1-8B</t>
+          <t>meta-llama/Meta-Llama-3-8B, meta-llama/Meta-Llama-3-8B-Instruct, beomi/Llama-3-Open-Ko-8B</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>LogicKor Single turn=8.69;LogicKor Multi turn=8.95</t>
+          <t>LogicKor_single=5.143;LogicKor_multi=5.238;KoBEST_boolq=85.47;KoBEST_copa=74.20;KoBEST_hellaswag=42.20;KoBEST_sentineg=94.71;KoBEST_wic=60.95</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -18877,7 +18881,7 @@
       <c r="V204" t="inlineStr"/>
       <c r="W204" t="inlineStr">
         <is>
-          <t>LogicKor Single turn=8.69;LogicKor Multi turn=8.95</t>
+          <t>LogicKor_single=5.143;LogicKor_multi=5.238;KoBEST_boolq=85.47;KoBEST_copa=74.20;KoBEST_hellaswag=42.20;KoBEST_sentineg=94.71;KoBEST_wic=60.95</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -18886,32 +18890,32 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>NCSOFT/Llama-3-OffsetBias-RM-8B</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Llama-3-OffsetBias-RM-8B</t>
+          <t>Llama-3-Alpha-Ko-8B-Instruct</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/Llama-3-OffsetBias-RM-8B</t>
+          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2407.06551</t>
+          <t>https://arxiv.org/abs/2403.07691</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>RewardBench Chat 97.21점의 고성능 리워드 모델로 RLHF 보상 신호 산출에 적합</t>
+          <t>LogicKor 6.62점으로 70B급 모델에 필적하는 성능을 달성해 복잡한 한국어 추론·대화 작업에 적합</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -18926,22 +18930,22 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>llama3</t>
+          <t>기타(llama3)</t>
         </is>
       </c>
       <c r="K205" s="2" t="n">
-        <v>45484</v>
+        <v>45435</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>45541</v>
+        <v>45436</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>7504928768</v>
+        <v>8030261248</v>
       </c>
       <c r="N205" s="3" t="inlineStr"/>
       <c r="O205" t="inlineStr">
@@ -18951,64 +18955,60 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>LlamaForSequenceClassification</t>
+          <t>LlamaForCausalLM</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>sfairXC/FsfairX-LLaMA3-RM-v0.1, meta-llama/Meta-Llama-3-8B-Instruct</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>RewardBench Chat=97.21;RewardBench Chat Hard=80.70;RewardBench Reasoning=90.60</t>
+          <t>LogicKor_single=7.143;LogicKor_multi=6.065;KoBEST_boolq=83.69;KoBEST_copa=74.20;KoBEST_hellaswag=42.40;KoBEST_sentineg=92.44;KoBEST_wic=57.30</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>RewardBench Safety=89.01;EvalBiasBench Length=82.4;EvalBiasBench Concreteness=92.9;EvalBiasBench Empty Reference=46.2;EvalBiasBench Content Continuation=100.0;EvalBiasBench Nested Instruction=83.3;EvalBiasBench Familiar Knowledge=58.3</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>LogicKor_single=7.143;LogicKor_multi=6.065;KoBEST_boolq=83.69;KoBEST_copa=74.20;KoBEST_hellaswag=42.40;KoBEST_sentineg=92.44;KoBEST_wic=57.30</t>
+        </is>
+      </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NCSOFT/Llama-3-OffsetBias-8B</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Llama-3-OffsetBias-8B</t>
+          <t>Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://huggingface.co/NCSOFT/Llama-3-OffsetBias-8B</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2407.06551</t>
-        </is>
-      </c>
+          <t>https://huggingface.co/allganize/Llama-3-Alpha-Ko-8B-Instruct-marlin</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>평가 편향에 강건하도록 학습된 LLM 심사 모델로 페어와이즈 응답 평가에 적합</t>
+          <t>LogicKor 6.30점(4bit Marlin, Ampere GPU 최적화)으로 성능 손실 최소화한 고속 추론에 적합</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -19023,27 +19023,27 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>영어</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>llama3</t>
+          <t>기타(llama3)</t>
         </is>
       </c>
       <c r="K206" s="2" t="n">
-        <v>45484</v>
+        <v>45435</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>45496</v>
+        <v>45436</v>
       </c>
       <c r="M206" s="3" t="n">
-        <v>8030261248</v>
+        <v>8000000000</v>
       </c>
       <c r="N206" s="3" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>BF16</t>
+          <t>INT4</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -19053,27 +19053,27 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-8B-Instruct</t>
+          <t>allganize/Llama-3-Alpha-Ko-8B-Evo</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>LLMBar Natural=86.5;LLMBar Neighbor=81.0;LLMBar GPTInst=91.8;LLMBar GPTOut=60.6;LLMBar Manual=71.7</t>
+          <t>LogicKor_single=6.857;LogicKor_multi=5.738</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>EvalBiasBench Length=85.3;EvalBiasBench Concreteness=100.0;EvalBiasBench Empty Reference=92.3;EvalBiasBench Content Continuation=95.8;EvalBiasBench Nested Instruction=50.0;EvalBiasBench Familiar Knowledge=83.3</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>LogicKor_single=6.857;LogicKor_multi=5.738</t>
+        </is>
+      </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr"/>
     </row>
@@ -44707,7 +44707,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -44805,7 +44805,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -44907,7 +44907,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -45001,7 +45001,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>알간이즈</t>
+          <t>올거나이즈</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -45099,7 +45099,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>데이터모</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -45193,7 +45193,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>데이터모</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -58613,7 +58613,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -58699,7 +58699,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -58787,7 +58787,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -58875,7 +58875,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -58963,7 +58963,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -59049,7 +59049,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>시오닉에이아이</t>
+          <t>사이오닉AI</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">

--- a/output/huggingface_models_2026-07-20.xlsx
+++ b/output/huggingface_models_2026-07-20.xlsx
@@ -450,7 +450,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="52" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3513,7 +3513,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R39" t="inlineStr"/>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R46" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5180,7 +5180,7 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5540,7 +5540,7 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5718,7 +5718,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5805,7 +5805,7 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5892,7 +5892,7 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R63" t="inlineStr"/>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R64" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R69" t="inlineStr"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7099,7 +7099,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7180,7 +7180,7 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R73" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R74" t="inlineStr"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R75" t="inlineStr"/>
@@ -7423,7 +7423,7 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R76" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R79" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8733,7 +8733,7 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8814,7 +8814,7 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8895,7 +8895,7 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8976,7 +8976,7 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9057,7 +9057,7 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -9138,7 +9138,7 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9219,7 +9219,7 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9300,7 +9300,7 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9381,7 +9381,7 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9462,7 +9462,7 @@
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9543,7 +9543,7 @@
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9624,7 +9624,7 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -10065,7 +10065,7 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -10150,7 +10150,7 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -10235,7 +10235,7 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -11210,7 +11210,7 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11380,7 +11380,7 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -11465,7 +11465,7 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -11550,7 +11550,7 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -11635,7 +11635,7 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -13097,7 +13097,7 @@
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R140" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R141" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R143" t="inlineStr"/>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R146" t="inlineStr"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -14527,7 +14527,7 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15826,7 +15826,7 @@
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -16194,7 +16194,7 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -16283,7 +16283,7 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -16372,7 +16372,7 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R187" t="inlineStr"/>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -18313,7 +18313,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>병합 모델</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>병합 모델</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -19053,7 +19053,7 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -19320,7 +19320,7 @@
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -19498,7 +19498,7 @@
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R213" t="inlineStr"/>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -20088,7 +20088,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -20187,7 +20187,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R221" t="inlineStr"/>
@@ -20591,7 +20591,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R222" t="inlineStr"/>
@@ -20684,7 +20684,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R226" t="inlineStr"/>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R227" t="inlineStr"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R228" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R229" t="inlineStr"/>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R230" t="inlineStr"/>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -21537,7 +21537,7 @@
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R232" t="inlineStr"/>
@@ -21610,7 +21610,7 @@
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R233" t="inlineStr"/>
@@ -21687,7 +21687,7 @@
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R234" t="inlineStr"/>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R235" t="inlineStr"/>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R236" t="inlineStr"/>
@@ -21934,7 +21934,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -22209,7 +22209,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -22375,7 +22375,7 @@
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -22460,7 +22460,7 @@
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -22549,7 +22549,7 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -22642,7 +22642,7 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R251" t="inlineStr"/>
@@ -23279,7 +23279,7 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -23633,7 +23633,7 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R257" t="inlineStr"/>
@@ -23831,7 +23831,7 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R263" t="inlineStr"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R264" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -24611,7 +24611,7 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -24809,7 +24809,7 @@
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R269" t="inlineStr"/>
@@ -25011,7 +25011,7 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -26031,7 +26031,7 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -26371,7 +26371,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -26541,7 +26541,7 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -27221,7 +27221,7 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -27405,7 +27405,7 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -27492,7 +27492,7 @@
       <c r="P299" t="inlineStr"/>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -27595,7 +27595,7 @@
       <c r="P300" t="inlineStr"/>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -27985,7 +27985,7 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -28367,7 +28367,7 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="R312" t="inlineStr"/>
@@ -28854,7 +28854,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -28947,7 +28947,7 @@
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R316" t="inlineStr"/>
@@ -29246,7 +29246,7 @@
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R318" t="inlineStr"/>
@@ -29428,7 +29428,7 @@
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R319" t="inlineStr"/>
@@ -29525,7 +29525,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -29618,7 +29618,7 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -30390,7 +30390,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -30493,7 +30493,7 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -30592,7 +30592,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -30877,7 +30877,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -30974,7 +30974,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -31059,7 +31059,7 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -31334,7 +31334,7 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -31433,7 +31433,7 @@
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -31528,7 +31528,7 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -32169,7 +32169,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -32269,7 +32269,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -32469,7 +32469,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -32663,7 +32663,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -32955,7 +32955,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -33163,7 +33163,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -33267,7 +33267,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -33471,7 +33471,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -33575,7 +33575,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -33675,7 +33675,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -33779,7 +33779,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -33983,7 +33983,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -34199,7 +34199,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -34307,7 +34307,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -34503,7 +34503,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -34705,7 +34705,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -34909,7 +34909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -34999,7 +34999,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -35179,7 +35179,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -35269,7 +35269,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -35363,7 +35363,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -35457,7 +35457,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -35549,7 +35549,7 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -35657,7 +35657,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -35881,7 +35881,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -35985,7 +35985,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -36089,7 +36089,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -36193,7 +36193,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -36301,7 +36301,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -36405,7 +36405,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -36511,7 +36511,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -36803,7 +36803,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
@@ -36905,7 +36905,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -37183,7 +37183,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -37371,7 +37371,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -37649,7 +37649,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -37743,7 +37743,7 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -37833,7 +37833,7 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -38021,7 +38021,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -38111,7 +38111,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -38205,7 +38205,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -38395,7 +38395,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S66" t="inlineStr"/>
@@ -38495,7 +38495,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -38587,7 +38587,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -38683,7 +38683,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
@@ -38783,7 +38783,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -38875,7 +38875,7 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S72" t="inlineStr"/>
@@ -39071,7 +39071,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -39163,7 +39163,7 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -39259,7 +39259,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
@@ -39367,7 +39367,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -39463,7 +39463,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -39555,7 +39555,7 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -39651,7 +39651,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -39747,7 +39747,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
@@ -39855,7 +39855,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -40043,7 +40043,7 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -40139,7 +40139,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -40343,7 +40343,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -40459,7 +40459,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -40567,7 +40567,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -40671,7 +40671,7 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -40771,7 +40771,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -40879,7 +40879,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -40987,7 +40987,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -41095,7 +41095,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S93" t="inlineStr"/>
@@ -41211,7 +41211,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -41323,7 +41323,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -41523,7 +41523,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -41717,7 +41717,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -41807,7 +41807,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -41897,7 +41897,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -41987,7 +41987,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -42077,7 +42077,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S106" t="inlineStr"/>
@@ -42483,7 +42483,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -42591,7 +42591,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -42697,7 +42697,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S109" t="inlineStr"/>
@@ -42801,7 +42801,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -42899,7 +42899,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
@@ -42985,7 +42985,7 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -43067,7 +43067,7 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S113" t="inlineStr"/>
@@ -43161,7 +43161,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -43255,7 +43255,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -43357,7 +43357,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>병합 모델</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -43651,7 +43651,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -43745,7 +43745,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -43851,7 +43851,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -43949,7 +43949,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -44057,7 +44057,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -44485,7 +44485,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -44575,7 +44575,7 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -44669,7 +44669,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -44763,7 +44763,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>병합 모델(mergekit 등)</t>
+          <t>병합 모델</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -45057,7 +45057,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -45159,7 +45159,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -45249,7 +45249,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -45443,7 +45443,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
@@ -45537,7 +45537,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -45631,7 +45631,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -45725,7 +45725,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -45819,7 +45819,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -45913,7 +45913,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -46007,7 +46007,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -46097,7 +46097,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -46187,7 +46187,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -46275,7 +46275,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -46361,7 +46361,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -46451,7 +46451,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -46629,7 +46629,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -46809,7 +46809,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -46899,7 +46899,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -46989,7 +46989,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -47079,7 +47079,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -47259,7 +47259,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -47349,7 +47349,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -47439,7 +47439,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -47529,7 +47529,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -47619,7 +47619,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -47709,7 +47709,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -47799,7 +47799,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -47889,7 +47889,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
@@ -47979,7 +47979,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -48069,7 +48069,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -48339,7 +48339,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -48429,7 +48429,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -48789,7 +48789,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -48883,7 +48883,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -48977,7 +48977,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -49167,7 +49167,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
@@ -49711,7 +49711,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -49809,7 +49809,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -49907,7 +49907,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -50273,7 +50273,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S192" t="inlineStr"/>
@@ -50449,7 +50449,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S193" t="inlineStr"/>
@@ -50527,7 +50527,7 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
@@ -50605,7 +50605,7 @@
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S195" t="inlineStr"/>
@@ -50687,7 +50687,7 @@
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
@@ -50771,7 +50771,7 @@
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -50879,7 +50879,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S198" t="inlineStr"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S199" t="inlineStr"/>
@@ -51087,7 +51087,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S200" t="inlineStr"/>
@@ -51191,7 +51191,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S201" t="inlineStr"/>
@@ -51295,7 +51295,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S202" t="inlineStr"/>
@@ -51399,7 +51399,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S203" t="inlineStr"/>
@@ -51499,7 +51499,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -51603,7 +51603,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
@@ -51711,7 +51711,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S206" t="inlineStr"/>
@@ -51815,7 +51815,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -51919,7 +51919,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
@@ -52023,7 +52023,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -52131,7 +52131,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
@@ -52235,7 +52235,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
@@ -52341,7 +52341,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S212" t="inlineStr"/>
@@ -52445,7 +52445,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
@@ -52539,7 +52539,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
@@ -52641,7 +52641,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
@@ -52735,7 +52735,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -52829,7 +52829,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -52923,7 +52923,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
@@ -53027,7 +53027,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -53121,7 +53121,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
@@ -53219,7 +53219,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
@@ -53317,7 +53317,7 @@
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S222" t="inlineStr"/>
@@ -53407,7 +53407,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S223" t="inlineStr"/>
@@ -53489,7 +53489,7 @@
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S224" t="inlineStr"/>
@@ -53571,7 +53571,7 @@
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S225" t="inlineStr"/>
@@ -53663,7 +53663,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S226" t="inlineStr"/>
@@ -53755,7 +53755,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
@@ -53859,7 +53859,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S228" t="inlineStr"/>
@@ -53963,7 +53963,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S229" t="inlineStr"/>
@@ -54055,7 +54055,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -54161,7 +54161,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -54253,7 +54253,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -54347,7 +54347,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -54437,7 +54437,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
@@ -54545,7 +54545,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -54647,7 +54647,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -54741,7 +54741,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
@@ -54831,7 +54831,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -54937,7 +54937,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -55043,7 +55043,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -55137,7 +55137,7 @@
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -55227,7 +55227,7 @@
       <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
@@ -55317,7 +55317,7 @@
       <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
@@ -55407,7 +55407,7 @@
       <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
@@ -55497,7 +55497,7 @@
       <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
@@ -55587,7 +55587,7 @@
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
@@ -55677,7 +55677,7 @@
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
@@ -55767,7 +55767,7 @@
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -55857,7 +55857,7 @@
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -55951,7 +55951,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
@@ -56037,7 +56037,7 @@
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -56123,7 +56123,7 @@
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
@@ -56209,7 +56209,7 @@
       <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -56303,7 +56303,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -56389,7 +56389,7 @@
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -56475,7 +56475,7 @@
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -56561,7 +56561,7 @@
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -56655,7 +56655,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -56741,7 +56741,7 @@
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
@@ -56827,7 +56827,7 @@
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
@@ -56913,7 +56913,7 @@
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -57007,7 +57007,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
@@ -57093,7 +57093,7 @@
       <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
@@ -57179,7 +57179,7 @@
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
@@ -57265,7 +57265,7 @@
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
@@ -57359,7 +57359,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -57453,7 +57453,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -57547,7 +57547,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -57641,7 +57641,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -57735,7 +57735,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -57829,7 +57829,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S271" t="inlineStr">
@@ -57923,7 +57923,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
@@ -58017,7 +58017,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S273" t="inlineStr">
@@ -58111,7 +58111,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S274" t="inlineStr">
@@ -58205,7 +58205,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S275" t="inlineStr">
@@ -58291,7 +58291,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S276" t="inlineStr">
@@ -58381,7 +58381,7 @@
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr">
         <is>
-          <t>어댑터(LoRA 등)</t>
+          <t>어댑터</t>
         </is>
       </c>
       <c r="S277" t="inlineStr">
@@ -58475,7 +58475,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S278" t="inlineStr">
@@ -58579,7 +58579,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
@@ -58665,7 +58665,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
@@ -59015,7 +59015,7 @@
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S284" t="inlineStr">
@@ -59103,7 +59103,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
@@ -59195,7 +59195,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S286" t="inlineStr"/>
@@ -59295,7 +59295,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S287" t="inlineStr"/>
@@ -59395,7 +59395,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S288" t="inlineStr">
@@ -59503,7 +59503,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S289" t="inlineStr">
@@ -59605,7 +59605,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S290" t="inlineStr">
@@ -59717,7 +59717,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S291" t="inlineStr"/>
@@ -59817,7 +59817,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S292" t="inlineStr"/>
@@ -59919,7 +59919,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S293" t="inlineStr"/>
@@ -60019,7 +60019,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S294" t="inlineStr"/>
@@ -60123,7 +60123,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
@@ -60231,7 +60231,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S296" t="inlineStr">
@@ -60325,7 +60325,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S297" t="inlineStr">
@@ -60415,7 +60415,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>경량화·증류 모델(더 큰 모델에서 Pruning/Knowledge Distillation)</t>
+          <t>경량화·증류 모델</t>
         </is>
       </c>
       <c r="S298" t="inlineStr">
@@ -60507,7 +60507,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S299" t="inlineStr">
@@ -60619,7 +60619,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S300" t="inlineStr"/>
@@ -60723,7 +60723,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S301" t="inlineStr"/>
@@ -60825,7 +60825,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S302" t="inlineStr">
@@ -60917,7 +60917,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S303" t="inlineStr">
@@ -61025,7 +61025,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S304" t="inlineStr">
@@ -61137,7 +61137,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S305" t="inlineStr"/>
@@ -61245,7 +61245,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S306" t="inlineStr">
@@ -61353,7 +61353,7 @@
       <c r="Q307" t="inlineStr"/>
       <c r="R307" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S307" t="inlineStr">
@@ -61463,7 +61463,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S308" t="inlineStr">
@@ -61561,7 +61561,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S309" t="inlineStr">
@@ -61661,7 +61661,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
@@ -61755,7 +61755,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S311" t="inlineStr">
@@ -61849,7 +61849,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
@@ -61935,7 +61935,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
@@ -62033,7 +62033,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S314" t="inlineStr">
@@ -62131,7 +62131,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
@@ -62225,7 +62225,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
@@ -62415,7 +62415,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>베이스 모델(프롬스크래치 사전학습)</t>
+          <t>베이스 모델</t>
         </is>
       </c>
       <c r="S318" t="inlineStr"/>
@@ -62515,7 +62515,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
@@ -62617,7 +62617,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
@@ -62711,7 +62711,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S321" t="inlineStr">
@@ -62807,7 +62807,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>포맷 변환·포팅(양자화 아닌 ONNX/safetensors 등 형식 변환만)</t>
+          <t>포맷 변환·포팅</t>
         </is>
       </c>
       <c r="S322" t="inlineStr">
@@ -62901,7 +62901,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S323" t="inlineStr">
@@ -62991,7 +62991,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S324" t="inlineStr">
@@ -63085,7 +63085,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S325" t="inlineStr">
@@ -63179,7 +63179,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S326" t="inlineStr">
@@ -63273,7 +63273,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S327" t="inlineStr">
@@ -63379,7 +63379,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S328" t="inlineStr">
@@ -63485,7 +63485,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S329" t="inlineStr">
@@ -63581,7 +63581,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S330" t="inlineStr">
@@ -63677,7 +63677,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S331" t="inlineStr">
@@ -63767,7 +63767,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S332" t="inlineStr">
@@ -63865,7 +63865,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S333" t="inlineStr">
@@ -63959,7 +63959,7 @@
       <c r="Q334" t="inlineStr"/>
       <c r="R334" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S334" t="inlineStr">
@@ -64057,7 +64057,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S335" t="inlineStr">
@@ -64155,7 +64155,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S336" t="inlineStr">
@@ -64253,7 +64253,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S337" t="inlineStr">
@@ -64347,7 +64347,7 @@
       <c r="Q338" t="inlineStr"/>
       <c r="R338" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S338" t="inlineStr">
@@ -64441,7 +64441,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -64539,7 +64539,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S340" t="inlineStr">
@@ -64633,7 +64633,7 @@
       <c r="Q341" t="inlineStr"/>
       <c r="R341" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S341" t="inlineStr">
@@ -64731,7 +64731,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>파인튜닝 모델(SFT·RLHF·DPO 등 추가학습)</t>
+          <t>파인튜닝 모델</t>
         </is>
       </c>
       <c r="S342" t="inlineStr">
@@ -64829,7 +64829,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S343" t="inlineStr">
@@ -64923,7 +64923,7 @@
       <c r="Q344" t="inlineStr"/>
       <c r="R344" t="inlineStr">
         <is>
-          <t>양자화 모델(GGUF/GPTQ/AWQ 등)</t>
+          <t>양자화 모델</t>
         </is>
       </c>
       <c r="S344" t="inlineStr">

--- a/output/huggingface_models_2026-07-20.xlsx
+++ b/output/huggingface_models_2026-07-20.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 32B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 4B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 8B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gemma 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Gemma 12B 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gemma 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Gemma 27B 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qwen2.5-VL 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Qwen2.5-VL 32B 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qwen2.5-VL 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Qwen2.5-VL 7B 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Llama2(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Llemma(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CoT Collection 184만 rationale 학습, Flan-T5보다 CoT 추론 우수해 제로샷 과제 해결에 적합</t>
+          <t>CoT Collection 184만 rationale로 학습한 11B 모델, Flan-T5보다 CoT 추론 우수해 제로샷 과제에 적합</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CoT Collection 184만 rationale 학습, Flan-T5보다 CoT 추론 우수해 제로샷 과제 해결에 적합</t>
+          <t>CoT Collection 184만 rationale로 학습한 3B 모델, Flan-T5보다 CoT 추론 우수해 제로샷 과제에 적합</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>AWQ 4비트로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>FP8로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>GGUF로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>고성능 32B 모델을 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
+          <t>EXAONE-3.5 32B 인스트럭트를 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>고성능 32B 모델을 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
+          <t>EXAONE-4.0 32B를 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7139,7 +7139,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성해 실시간 음성 대화 시스템에 적합</t>
+          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성하는 1B 모델, 실시간 음성 대화 시스템에 적합</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7216,7 +7216,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성해 실시간 음성 대화 시스템에 적합</t>
+          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성하는 2B 모델, 실시간 음성 대화 시스템에 적합</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>대화체 음성을 실시간에 가깝게 생성하고 웃음·기침 등 비언어적 표현까지 지원, 리서치·교육용 대화형 TTS에 적합</t>
+          <t>대화체 음성을 실시간에 가깝게 생성, 웃음·기침 등 비언어적 표현까지 지원하는 리서치·교육용 대화형 TTS 0626 개정판</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>대화체 음성을 실시간에 가깝게 생성하고 웃음·기침 등 비언어적 표현까지 지원, 리서치·교육용 대화형 TTS에 적합</t>
+          <t>대화체 음성을 실시간에 가깝게 생성, 웃음·기침 등 비언어적 표현까지 지원하는 리서치·교육용 대화형 TTS 초기판</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8692,7 +8692,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8773,7 +8773,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8854,7 +8854,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8935,7 +8935,7 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9016,7 +9016,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9097,7 +9097,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9178,7 +9178,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9259,7 +9259,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9340,7 +9340,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9421,7 +9421,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9502,7 +9502,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9583,7 +9583,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 1.5B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 2.7B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 3.7B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Base 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Small 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Tiny 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류해 유사 품질을 내는 경량 텍스트-이미지 모델</t>
+          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류한 Base 크기 경량 텍스트-이미지 모델</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Base 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류해 유사 품질을 내는 경량 텍스트-이미지 모델</t>
+          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류한 Small 크기 경량 텍스트-이미지 모델</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Small 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Tiny 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -12720,7 +12720,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v2.1, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -12805,7 +12805,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v2.0, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -12890,7 +12890,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v1.1, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -12975,7 +12975,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v1.15, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>EEVE 방식으로 한국어 어휘를 확장 학습한 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -17156,7 +17156,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>SOLAR 기반으로 한국어 어휘를 확장 학습한 KoSOLAR 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -18268,7 +18268,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM(원본 구조), 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM의 HF transformers 호환판, 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -19938,7 +19938,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Kanana-2 미드트레이닝 체크포인트, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
+          <t>Kanana-2 30B-A3B의 미드트레이닝 체크포인트(2601), base 대비 추가 학습분 반영해 성능 향상</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -20239,7 +20239,7 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kanana-2 미드트레이닝 체크포인트, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
+          <t>Kanana-2 30B-A3B 베이스 모델, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화, 32K(YaRN 128K) 문맥 지원해 긴 문서 처리에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화한 2.1B 베이스, 32K(YaRN 128K) 문맥의 긴 문서 처리에 적합</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화된 인스트럭트 모델, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화한 2.1B 인스트럭트, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화, 32K(YaRN 128K) 문맥 지원해 긴 문서 처리에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화한 8B 베이스, 32K(YaRN 128K) 문맥의 긴 문서 처리에 적합</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화된 인스트럭트 모델, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화한 8B 인스트럭트, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -24473,7 +24473,7 @@
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, 다국어 VLM 연구에 적합</t>
+          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수(BF16), 다국어 VLM 연구에 적합</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -24566,7 +24566,7 @@
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, 다국어 VLM 연구에 적합</t>
+          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, FP16 변환판, 다국어 VLM 연구에 적합</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -26071,7 +26071,7 @@
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 0.6B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -26156,7 +26156,7 @@
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 4B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -26241,7 +26241,7 @@
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 8B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -26326,7 +26326,7 @@
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 0.6B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -26411,7 +26411,7 @@
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 4B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -26496,7 +26496,7 @@
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 8B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -26581,7 +26581,7 @@
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 2B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -26666,7 +26666,7 @@
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 32B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -26751,7 +26751,7 @@
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 4B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -30034,7 +30034,7 @@
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 70B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -30240,7 +30240,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 8B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 70B-Instruct를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 8B-Instruct를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -30545,7 +30545,7 @@
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 70B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -30640,7 +30640,7 @@
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -30735,7 +30735,7 @@
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B(Base)를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -30830,7 +30830,7 @@
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 70B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -30929,7 +30929,7 @@
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 대규모 모델의 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x22B(Base)를 FP8 양자화해 정확도를 유지하며 초대형 모델의 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -31014,7 +31014,7 @@
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 대규모 모델의 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x22B-Instruct를 FP8 양자화해 정확도를 유지하며 초대형 모델의 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -31099,7 +31099,7 @@
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x7B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -31188,7 +31188,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 13B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -31287,7 +31287,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 70B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 7B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mistral 7B-Instruct(v0.2)를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -31671,7 +31671,7 @@
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x7B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 13B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 70B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -33116,7 +33116,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-2 7B-Chat을 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -33424,7 +33424,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 70B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -33528,7 +33528,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 70B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -33628,7 +33628,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -33732,7 +33732,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -33832,7 +33832,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3 8B(Base)를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -33936,7 +33936,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 70B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 70B-Instruct를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 8B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -34260,7 +34260,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INT8 양자화로 추론 효율을 크게 높이면서 정확도는 유지해 경량 배포에 적합</t>
+          <t>Llama-3.1 8B-Instruct를 INT8 양자화해 추론 효율을 높이면서 정확도는 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mistral 7B-Instruct(v0.2)를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -34954,7 +34954,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 대규모 모델의 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x22B-Instruct를 FP8 양자화해 정확도를 유지하며 초대형 모델의 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -35044,7 +35044,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 대규모 모델의 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x22B(Base)를 FP8 양자화해 정확도를 유지하며 초대형 모델의 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -35134,7 +35134,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x7B-Instruct를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -35224,7 +35224,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FP8 양자화로 추론 효율을 높이면서 정확도를 유지해 경량 배포에 적합하다.</t>
+          <t>Mixtral 8x7B(Base)를 FP8 양자화해 추론 효율을 높이면서 정확도를 유지, 경량 배포에 적합</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>고성능 32B 모델을 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
+          <t>EXAONE-3.5 32B 인스트럭트를 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -39808,7 +39808,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>고성능 32B 모델을 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
+          <t>EXAONE-4.0 32B를 AWQ 4비트로 양자화해 메모리 절약하며 배포 가능</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -40412,7 +40412,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>AWQ 4비트로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>FP8로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>문서 이해·한국어 맥락 추론에서 동급 최고 성능인 비전언어모델, 한국어 문서 분석에 적합</t>
+          <t>GGUF로 양자화한 EXAONE-4.5 VLM, 문서 이해·한국어 맥락 추론에서 동급 최고 성능, 한국어 문서 분석에 적합</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -41672,7 +41672,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v1.1, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -41762,7 +41762,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v1.15, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -41852,7 +41852,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v2.0, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -41942,7 +41942,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>한국어 RAG(검색증강생성) 전용 데이터셋으로 QLoRA 파인튜닝되어 RAG 기반 한국어 질의응답에 적합</t>
+          <t>한국어 RAG 전용 데이터셋으로 QLoRA 파인튜닝한 v2.1, RAG 기반 한국어 질의응답에 적합</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -43512,7 +43512,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM(원본 구조), 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -43606,7 +43606,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM으로 문서·이미지 이해 작업에 적합</t>
+          <t>OCR·그라운딩·레퍼링을 지원하는 한영 VLM의 HF transformers 호환판, 문서·이미지 이해 작업에 적합</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -45398,7 +45398,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 32B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -45492,7 +45492,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 4B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -45586,7 +45586,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>GRPO로 다중홉 공간추론에 특화 학습되어 순차적 위치·방향 추론 질의응답에 적합</t>
+          <t>GRPO로 다중홉 공간추론에 특화 학습한 8B 모델, 순차적 위치·방향 추론 질의응답에 적합</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -45680,7 +45680,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gemma 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Gemma 12B 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -45774,7 +45774,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Gemma 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Gemma 27B 기반 VLM에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -45868,7 +45868,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Qwen2.5-VL 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Qwen2.5-VL 32B 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -45962,7 +45962,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Qwen2.5-VL 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
+          <t>Qwen2.5-VL 7B 기반에 이미지 안전분류(20종) 기능을 내장, 유해 콘텐츠 탐지·모더레이션에 적합</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -47214,7 +47214,7 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 0.6B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -47304,7 +47304,7 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 4B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -47394,7 +47394,7 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MRL 지원으로 임베딩 차원 축소가 가능해 유연한 의미 검색·유사도 매칭에 적합</t>
+          <t>MRL 지원으로 임베딩 차원 축소가 가능한 8B 임베딩 모델, 유연한 의미 검색·유사도 매칭에 적합</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -47484,7 +47484,7 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 0.6B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -47574,7 +47574,7 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 4B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -47664,7 +47664,7 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>쿼리-문서 관련도 점수를 산출해 RAG·검색 파이프라인의 재순위화 단계에 적합</t>
+          <t>쿼리-문서 관련도 점수를 산출하는 8B 리랭커, RAG·검색 파이프라인의 재순위화 단계에 적합</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -47754,7 +47754,7 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 2B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -47844,7 +47844,7 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 32B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -47934,7 +47934,7 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점이 있어 시각 문서 처리 작업에 적합</t>
+          <t>OCR·문서 및 차트 분석·공간추론·영상이해에 강점 있는 4B VLM, 시각 문서 처리 작업에 적합</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -48298,7 +48298,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>CoT Collection 184만 rationale 학습, Flan-T5보다 CoT 추론 우수해 제로샷 과제 해결에 적합</t>
+          <t>CoT Collection 184만 rationale로 학습한 11B 모델, Flan-T5보다 CoT 추론 우수해 제로샷 과제에 적합</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>CoT Collection 184만 rationale 학습, Flan-T5보다 CoT 추론 우수해 제로샷 과제 해결에 적합</t>
+          <t>CoT Collection 184만 rationale로 학습한 3B 모델, Flan-T5보다 CoT 추론 우수해 제로샷 과제에 적합</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -48478,7 +48478,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -48568,7 +48568,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48658,7 +48658,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>mT5 인코더와 Code Llama를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Code Llama(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -49216,7 +49216,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Llama2(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -49306,7 +49306,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Llemma(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -49396,7 +49396,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -49486,7 +49486,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -49576,7 +49576,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 MetaMath(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -49960,7 +49960,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 15B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -50050,7 +50050,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 20B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>mT5 인코더와 대상 LM을 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
+          <t>mT5 인코더와 Orca2(약 9B)를 결합, 다국어 데이터 없이도 다국어 추론 과제 해결에 강점</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -51040,7 +51040,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화, 32K(YaRN 128K) 문맥 지원해 긴 문서 처리에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화한 2.1B 베이스, 32K(YaRN 128K) 문맥의 긴 문서 처리에 적합</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화된 인스트럭트 모델, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화한 2.1B 인스트럭트, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -51248,7 +51248,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화, 32K(YaRN 128K) 문맥 지원해 긴 문서 처리에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 대폭 강화한 8B 베이스, 32K(YaRN 128K) 문맥의 긴 문서 처리에 적합</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -51352,7 +51352,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화된 인스트럭트 모델, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
+          <t>이전 버전 대비 코딩·수학·함수호출 능력 강화한 8B 인스트럭트, 32K 문맥 지원해 실전 대화·툴콜에 적합</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -51556,7 +51556,7 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Kanana-2 미드트레이닝 체크포인트, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
+          <t>Kanana-2 30B-A3B 베이스 모델, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -51976,7 +51976,7 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Kanana-2 미드트레이닝 체크포인트, 32.5B 이전모델보다 적은 활성파라미터로 32K 문맥·수학·코딩 성능 향상</t>
+          <t>Kanana-2 30B-A3B의 미드트레이닝 체크포인트(2601), base 대비 추가 학습분 반영해 성능 향상</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -53276,7 +53276,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>대화체 음성을 실시간에 가깝게 생성하고 웃음·기침 등 비언어적 표현까지 지원, 리서치·교육용 대화형 TTS에 적합</t>
+          <t>대화체 음성을 실시간에 가깝게 생성, 웃음·기침 등 비언어적 표현까지 지원하는 리서치·교육용 대화형 TTS 초기판</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -53362,7 +53362,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>대화체 음성을 실시간에 가깝게 생성하고 웃음·기침 등 비언어적 표현까지 지원, 리서치·교육용 대화형 TTS에 적합</t>
+          <t>대화체 음성을 실시간에 가깝게 생성, 웃음·기침 등 비언어적 표현까지 지원하는 리서치·교육용 대화형 TTS 0626 개정판</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -53448,7 +53448,7 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성해 실시간 음성 대화 시스템에 적합</t>
+          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성하는 1B 모델, 실시간 음성 대화 시스템에 적합</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -53530,7 +53530,7 @@
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성해 실시간 음성 대화 시스템에 적합</t>
+          <t>문장 전체 없이 실시간 스트리밍으로 대화 음성을 생성하는 2B 모델, 실시간 음성 대화 시스템에 적합</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -55096,7 +55096,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류해 유사 품질을 내는 경량 텍스트-이미지 모델</t>
+          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류한 Base 크기 경량 텍스트-이미지 모델</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -55186,7 +55186,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Base 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -55276,7 +55276,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류해 유사 품질을 내는 경량 텍스트-이미지 모델</t>
+          <t>SD v1.4 대비 0.1% 미만 데이터만으로 지식증류한 Small 크기 경량 텍스트-이미지 모델</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -55366,7 +55366,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Small 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -55546,7 +55546,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>이전 대비 10배 많은 LAION 데이터로 사전학습해 이미지 생성 품질 향상, 경량 텍스트-이미지 모델</t>
+          <t>이전 대비 10배 많은 LAION 데이터로 사전학습한 Tiny 크기 경량 텍스트-이미지 모델, 이미지 생성 품질 향상</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -55636,7 +55636,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Base 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -55726,7 +55726,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Small 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SD-v2.1-base를 지식증류로 압축, 배치 축소로 학습 속도를 높인 경량 텍스트-이미지 모델</t>
+          <t>SD-v2.1-base를 지식증류로 압축한 Tiny 크기 경량 텍스트-이미지 모델, 배치 축소로 학습 속도 향상</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -55906,7 +55906,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 1.5B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -55996,7 +55996,7 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -56082,7 +56082,7 @@
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -56168,7 +56168,7 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 1.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -56258,7 +56258,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 2.7B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -56348,7 +56348,7 @@
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -56434,7 +56434,7 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -56520,7 +56520,7 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 2.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -56610,7 +56610,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Vicuna-7B를 프루닝·LoRA로 경량화, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
+          <t>Vicuna-7B를 프루닝·LoRA로 경량화한 3.7B 버전, GPU 1장으로 수 시간 내 저비용 재학습 가능</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -56700,7 +56700,7 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -56786,7 +56786,7 @@
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -56872,7 +56872,7 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 3.7B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -57052,7 +57052,7 @@
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC 포맷(FP16)으로 변환한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -57138,7 +57138,7 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_0)로 양자화한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -57224,7 +57224,7 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MLC-LLM·WebLLM에서 바로 구동 가능한 포맷으로 변환해 온디바이스·웹 배포에 적합</t>
+          <t>Vicuna 프루닝 모델을 MLC용 INT4(q4f16_1)로 양자화한 5.5B 버전, 온디바이스·웹 배포에 적합</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -61418,7 +61418,7 @@
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, 다국어 VLM 연구에 적합</t>
+          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수(BF16), 다국어 VLM 연구에 적합</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -61516,7 +61516,7 @@
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, 다국어 VLM 연구에 적합</t>
+          <t>영어 데이터만으로 학습했음에도 한국어 시각추론에서 LLaVA 대비 우수, FP16 변환판, 다국어 VLM 연구에 적합</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -62946,7 +62946,7 @@
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>SOLAR 기반으로 한국어 어휘를 확장 학습한 KoSOLAR 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -63040,7 +63040,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>한국어 어휘를 확장 학습해 한국어 능력을 강화한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>EEVE 방식으로 한국어 어휘를 확장 학습한 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">

--- a/output/huggingface_models_2026-07-20.xlsx
+++ b/output/huggingface_models_2026-07-20.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>다국어(196개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(196개 언어)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>다국어(31개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(31개 언어)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>다국어(5개 언어)</t>
+          <t>한국어, 영어, 다국어(5개 언어)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -23700,7 +23700,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -24197,7 +24197,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -25244,7 +25244,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -27373,7 +27373,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>다국어(24개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(24개 언어)</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -30358,7 +30358,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -30461,7 +30461,7 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>다국어(10개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(10개 언어)</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
@@ -34059,7 +34059,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -34167,7 +34167,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -34275,7 +34275,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -35629,7 +35629,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -36057,7 +36057,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>다국어(24개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(24개 언어)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>다국어(10개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(10개 언어)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -39335,7 +39335,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -39527,7 +39527,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -39619,7 +39619,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -39823,7 +39823,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -39919,7 +39919,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -40015,7 +40015,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -40203,7 +40203,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -40311,7 +40311,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -40427,7 +40427,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -40535,7 +40535,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -40643,7 +40643,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -41063,7 +41063,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -41291,7 +41291,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -44299,7 +44299,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>다국어(5개 언어)</t>
+          <t>한국어, 영어, 다국어(5개 언어)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -44377,7 +44377,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>다국어(31개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(31개 언어)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -46157,7 +46157,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>다국어(6개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(6개 언어)</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -46421,7 +46421,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>다국어(8개 언어)</t>
+          <t>영어, 다국어(8개 언어)</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -48493,7 +48493,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -48583,7 +48583,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -48673,7 +48673,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -49321,7 +49321,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -49501,7 +49501,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -49591,7 +49591,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -50065,7 +50065,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -50155,7 +50155,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>다국어(102개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(102개 언어)</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -59075,7 +59075,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>다국어(196개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(196개 언어)</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -60385,7 +60385,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -60475,7 +60475,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -60587,7 +60587,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -60691,7 +60691,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -60795,7 +60795,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -60885,7 +60885,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -60993,7 +60993,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>다국어(3개 언어)</t>
+          <t>한국어, 영어, 일본어, 다국어(3개 언어)</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -61105,7 +61105,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -61213,7 +61213,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -61325,7 +61325,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>다국어(4개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(4개 언어)</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -63737,7 +63737,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -63835,7 +63835,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -63933,7 +63933,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -64027,7 +64027,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -64125,7 +64125,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -64223,7 +64223,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -64321,7 +64321,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -64411,7 +64411,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>다국어(11개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(11개 언어)</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -64509,7 +64509,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -64607,7 +64607,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -64701,7 +64701,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -64897,7 +64897,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>다국어(32개 언어)</t>
+          <t>한국어, 영어, 일본어, 중국어, 다국어(32개 언어)</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">

--- a/output/huggingface_models_2026-07-20.xlsx
+++ b/output/huggingface_models_2026-07-20.xlsx
@@ -443,7 +443,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="57" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>기타(k-exaone)</t>
+          <t>기타(K-EXAONE AI Model License Agreement)</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>기타(hyperclovax)</t>
+          <t>기타(HyperCLOVA X SEED 32B Think Model License Agreement)</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델로, 다국어 프로덕션 번역 파이프라인에 적합합니다.</t>
+          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델, 다국어 프로덕션 번역 파이프라인에 적합</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델로, 경량 배포 환경에 적합합니다.</t>
+          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델, 경량 배포 환경에 적합</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델입니다.</t>
+          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델입니다.</t>
+          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델로, 효율적 추론 배포에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델, 효율적 추론 배포에 적합</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공해 로컬 추론에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델입니다.</t>
+          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델입니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적 번역 배포에 적합합니다.</t>
+          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적인 번역 배포에 적합</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판입니다.</t>
+          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델입니다.</t>
+          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -16416,7 +16416,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델입니다.</t>
+          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델입니다.</t>
+          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16598,7 +16598,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델입니다.</t>
+          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델로, 한국어 대화 어시스턴트 용도에 적합합니다.</t>
+          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델, 한국어 대화 어시스턴트 용도에 적합</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델로, 경량 한국어 어시스턴트 용도에 적합합니다.</t>
+          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델, 경량 한국어 어시스턴트 용도에 적합</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델로, 해당 작업에 활용하기 적합합니다.</t>
+          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델, 해당 작업 활용에 적합</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>기타(upstage-solar-license)</t>
+          <t>기타(Upstage Solar License)</t>
         </is>
       </c>
       <c r="K187" s="2" t="n">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>8B로 OpenCompass 70.2점을 내며 실시간 음성 대화와 멀티모달 라이브 스트리밍이 가능하다.</t>
+          <t>8B로 OpenCompass 70.2점을 내며 실시간 음성 대화·멀티모달 라이브 스트리밍에 강점</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -27358,7 +27358,7 @@
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>최고 수준 에이전틱·함수 호출 능력을 갖춘 41B 활성 파라미터 모델로 엔터프라이즈 지식업무에 적합하다.</t>
+          <t>최고 수준 에이전틱·함수 호출 능력을 갖춘 41B 활성 파라미터 모델로 엔터프라이즈 지식업무에 적합</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3.5B 활성 파라미터 MoE로 MiniF2F 수학 증명과 최대 1M 토큰 장문맥에 강하다.</t>
+          <t>3.5B 활성 파라미터 MoE로 MiniF2F 수학 증명과 최대 1M 토큰 장문맥에 강점</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>BF16 대비 정확도 손실이 미미한 FP8 양자화 버전으로 효율적인 배포에 적합하다.</t>
+          <t>BF16 대비 정확도 손실이 미미한 FP8 양자화 버전으로 효율적인 배포에 적합</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>음성인식 리더보드 1위(WER 6.14%)를 기록하며 오픈소스 최초로 음성 요약을 지원한다.</t>
+          <t>음성인식 리더보드 1위(WER 6.14%)를 기록, 오픈소스 최초로 음성 요약 지원</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -28213,7 +28213,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>1M 토큰 컨텍스트를 지원하고 추론 연산량을 R1 대비 25%로 줄여 장문·고난도 추론에 적합하다.</t>
+          <t>1M 토큰 컨텍스트를 지원하고 추론 연산량을 R1 대비 25%로 줄여 장문·고난도 추론에 적합</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -28320,7 +28320,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>7.6B 중 2.4B만 활성화하는 경량 MoE로 메모리·연산 제약 환경에 적합하다.</t>
+          <t>7.6B 중 2.4B만 활성화하는 경량 MoE로 메모리·연산 제약 환경에 적합</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>3.8B 중 1.1B만 활성화하는 초경량 MoE로 메모리·연산 제약 환경에 적합하다.</t>
+          <t>3.8B 중 1.1B만 활성화하는 초경량 MoE로 메모리·연산 제약 환경에 적합</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>7B 경량모델로 GSM8K 89.6점 등 수학·추론에서 동급 이상 성능을 낸다.</t>
+          <t>7B 경량모델로 GSM8K 89.6점 등 수학·추론에서 동급 이상 성능</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>함수 호출과 코드 인터프리터, 에이전트 작업을 기본 지원해 복잡한 도구 연동에 적합하다.</t>
+          <t>함수 호출과 코드 인터프리터, 에이전트 작업을 기본 지원해 복잡한 도구 연동에 적합</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>8B 모델로 OpenCompass 65.2점을 기록해 GPT-4V를 능가하며 온디바이스 구동도 가능하다.</t>
+          <t>8B 모델로 OpenCompass 65.2점을 기록해 GPT-4V를 능가, 온디바이스 구동에도 적합</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -29573,7 +29573,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>오픈소스이면서 GPT-4V와 GPT-4o 사이 수준의 성능을 보여 범용 이미지 이해에 적합하다.</t>
+          <t>오픈소스이면서 GPT-4V와 GPT-4o 사이 수준의 성능을 보여 범용 이미지 이해에 적합</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -29662,7 +29662,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GPT-4V와 GPT-4o 사이 성능의 오픈소스 비전-언어 모델로 범용 이미지 이해에 적합하다.</t>
+          <t>GPT-4V와 GPT-4o 사이 성능의 오픈소스 비전-언어 모델로 범용 이미지 이해에 적합</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -29751,7 +29751,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>4.2B의 경량 모델이지만 ScienceQA·ChartQA에서 GPT-4V-Turbo를 능가한다.</t>
+          <t>4.2B의 경량 모델이지만 ScienceQA·ChartQA에서 GPT-4V-Turbo를 능가하는 성능</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -29850,7 +29850,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>다중 이미지·영상 비교와 요약이 가능하며 BLINK 벤치마크에서 동급 모델을 능가한다.</t>
+          <t>다중 이미지·영상 비교와 요약이 가능하며 BLINK 벤치마크에서 동급 모델을 능가</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -31481,7 +31481,7 @@
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>RAG와 멀티스텝 툴 유즈에 특화된 104B 다국어 모델로 에이전트형 업무에 적합하다.</t>
+          <t>RAG와 멀티스텝 툴 유즈에 특화된 104B 다국어 모델, 에이전트형 업무에 강점</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -31845,7 +31845,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="57" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -34458,7 +34458,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8B 모델로 OpenCompass 65.2점을 기록해 GPT-4V를 능가하며 온디바이스 구동도 가능하다.</t>
+          <t>8B 모델로 OpenCompass 65.2점을 기록해 GPT-4V를 능가, 온디바이스 구동에도 적합</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8B로 OpenCompass 70.2점을 내며 실시간 음성 대화와 멀티모달 라이브 스트리밍이 가능하다.</t>
+          <t>8B로 OpenCompass 70.2점을 내며 실시간 음성 대화·멀티모달 라이브 스트리밍에 강점</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -34658,7 +34658,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1M 토큰 컨텍스트를 지원하고 추론 연산량을 R1 대비 25%로 줄여 장문·고난도 추론에 적합하다.</t>
+          <t>1M 토큰 컨텍스트를 지원하고 추론 연산량을 R1 대비 25%로 줄여 장문·고난도 추론에 적합</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -34862,7 +34862,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>최고 수준 에이전틱·함수 호출 능력을 갖춘 41B 활성 파라미터 모델로 엔터프라이즈 지식업무에 적합하다.</t>
+          <t>최고 수준 에이전틱·함수 호출 능력을 갖춘 41B 활성 파라미터 모델로 엔터프라이즈 지식업무에 적합</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>오픈소스이면서 GPT-4V와 GPT-4o 사이 수준의 성능을 보여 범용 이미지 이해에 적합하다.</t>
+          <t>오픈소스이면서 GPT-4V와 GPT-4o 사이 수준의 성능을 보여 범용 이미지 이해에 적합</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -35412,7 +35412,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GPT-4V와 GPT-4o 사이 성능의 오픈소스 비전-언어 모델로 범용 이미지 이해에 적합하다.</t>
+          <t>GPT-4V와 GPT-4o 사이 성능의 오픈소스 비전-언어 모델로 범용 이미지 이해에 적합</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.5B 활성 파라미터 MoE로 MiniF2F 수학 증명과 최대 1M 토큰 장문맥에 강하다.</t>
+          <t>3.5B 활성 파라미터 MoE로 MiniF2F 수학 증명과 최대 1M 토큰 장문맥에 강점</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -35614,7 +35614,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BF16 대비 정확도 손실이 미미한 FP8 양자화 버전으로 효율적인 배포에 적합하다.</t>
+          <t>BF16 대비 정확도 손실이 미미한 FP8 양자화 버전으로 효율적인 배포에 적합</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7B 경량모델로 GSM8K 89.6점 등 수학·추론에서 동급 이상 성능을 낸다.</t>
+          <t>7B 경량모델로 GSM8K 89.6점 등 수학·추론에서 동급 이상 성능</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -35834,7 +35834,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.2B의 경량 모델이지만 ScienceQA·ChartQA에서 GPT-4V-Turbo를 능가한다.</t>
+          <t>4.2B의 경량 모델이지만 ScienceQA·ChartQA에서 GPT-4V-Turbo를 능가하는 성능</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>다중 이미지·영상 비교와 요약이 가능하며 BLINK 벤치마크에서 동급 모델을 능가한다.</t>
+          <t>다중 이미지·영상 비교와 요약이 가능하며 BLINK 벤치마크에서 동급 모델을 능가</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>음성인식 리더보드 1위(WER 6.14%)를 기록하며 오픈소스 최초로 음성 요약을 지원한다.</t>
+          <t>음성인식 리더보드 1위(WER 6.14%)를 기록, 오픈소스 최초로 음성 요약 지원</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7.6B 중 2.4B만 활성화하는 경량 MoE로 메모리·연산 제약 환경에 적합하다.</t>
+          <t>7.6B 중 2.4B만 활성화하는 경량 MoE로 메모리·연산 제약 환경에 적합</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -36254,7 +36254,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.8B 중 1.1B만 활성화하는 초경량 MoE로 메모리·연산 제약 환경에 적합하다.</t>
+          <t>3.8B 중 1.1B만 활성화하는 초경량 MoE로 메모리·연산 제약 환경에 적합</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -36358,7 +36358,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>RAG와 멀티스텝 툴 유즈에 특화된 104B 다국어 모델로 에이전트형 업무에 적합하다.</t>
+          <t>RAG와 멀티스텝 툴 유즈에 특화된 104B 다국어 모델, 에이전트형 업무에 강점</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -36466,7 +36466,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>함수 호출과 코드 인터프리터, 에이전트 작업을 기본 지원해 복잡한 도구 연동에 적합하다.</t>
+          <t>함수 호출과 코드 인터프리터, 에이전트 작업을 기본 지원해 복잡한 도구 연동에 적합</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -41068,7 +41068,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>기타(k-exaone)</t>
+          <t>기타(K-EXAONE AI Model License Agreement)</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
@@ -53936,7 +53936,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>기타(hyperclovax)</t>
+          <t>기타(HyperCLOVA X SEED 32B Think Model License Agreement)</t>
         </is>
       </c>
       <c r="L229" s="2" t="n">
@@ -62388,7 +62388,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>기타(upstage-solar-license)</t>
+          <t>기타(Upstage Solar License)</t>
         </is>
       </c>
       <c r="L318" s="2" t="n">
@@ -63134,7 +63134,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델로, 추가 파인튜닝의 기반으로 적합합니다.</t>
+          <t>경량 2.8B 모델에 한국어 어휘를 확장 학습한 베이스 모델, 추가 파인튜닝의 기반으로 적합</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -63228,7 +63228,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델로, 한국어 대화 어시스턴트 용도에 적합합니다.</t>
+          <t>Open LLM Leaderboard 평균 66.48점(GSM8K 50.72)을 기록한 한국어 채팅 모델, 한국어 대화 어시스턴트 용도에 적합</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -63334,7 +63334,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델로, 경량 한국어 어시스턴트 용도에 적합합니다.</t>
+          <t>Open LLM Leaderboard 평균 58.71점을 기록한 소형 한국어 채팅 모델, 경량 한국어 어시스턴트 용도에 적합</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -63440,7 +63440,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델로, 해당 작업에 활용하기 적합합니다.</t>
+          <t>수학·코딩·영한 번역에 강점이 있다고 소개된 프리뷰 하이브리드 추론 모델, 해당 작업 활용에 적합</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -63534,7 +63534,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델로, 다국어 프로덕션 번역 파이프라인에 적합합니다.</t>
+          <t>JSON·YAML·XML 등 구조화 데이터의 스키마를 보존하며 번역하는 특화 모델, 다국어 프로덕션 번역 파이프라인에 적합</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -63630,7 +63630,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델로, 경량 배포 환경에 적합합니다.</t>
+          <t>비FP8 버전보다 더 빠르고 가벼운 추론을 위한 FP8 양자화 번역 모델, 경량 배포 환경에 적합</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -63722,7 +63722,7 @@
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델입니다.</t>
+          <t>120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 34.75점의 번역 품질을 12B 규모로 달성한 효율적 모델</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -63820,7 +63820,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델입니다.</t>
+          <t>GPT-4o(36.08)·Gemini-2.5-flash(35.25)보다 높은 WMT24++ CHrF++ 37.36점을 기록한 12B 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -63918,7 +63918,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판입니다.</t>
+          <t>GPT-4o(36.08)·Gemini(35.25)보다 높은 WMT24++ 영한 번역 CHrF++ 37.36점을 기록한 GGUF 경량 배포판</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -64012,7 +64012,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델입니다.</t>
+          <t>gpt-oss-120b(31.51)·gemini-2.0-flash(33.81)보다 높은 CHrF++ 33.87점을 20B 규모로 달성한 효율적 번역 모델</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -64110,7 +64110,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델입니다.</t>
+          <t>gpt-4o(36.08)·gemini-2.5-flash(35.25)를 능가하는 CHrF++ 37.21점의 27B 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -64208,7 +64208,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델로, 효율적 추론 배포에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 품질을 갖춘 FP8 경량 양자화 모델, 효율적 추론 배포에 적합</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -64306,7 +64306,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공해 로컬 추론에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 37.21점의 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -64396,7 +64396,7 @@
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
-          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델입니다.</t>
+          <t>4B 크기로 20B 규모 gpt-oss-20b(30.56)보다 높은 CHrF++ 31.31점을 달성한 경량 번역 모델</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -64494,7 +64494,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델입니다.</t>
+          <t>4B 크기로 gpt-oss-120b(31.51)와 자사 12B/20B 모델보다 높은 CHrF++ 35.09점을 달성한 고효율 번역 모델</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -64592,7 +64592,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델입니다.</t>
+          <t>4B 크기로 120B 규모 gpt-oss-120b(31.51)보다 높은 CHrF++ 35.09점을 달성한 GGUF 경량 번역 모델</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -64686,7 +64686,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델입니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점을 4B 규모로 달성한 고효율 구조화 데이터 번역 모델</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -64784,7 +64784,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적 번역 배포에 적합합니다.</t>
+          <t>gpt-4o(36.08) 다음으로 높은 CHrF++ 35.64점을 4B FP8 경량 모델로 달성해 효율적인 번역 배포에 적합</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -64882,7 +64882,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합합니다.</t>
+          <t>gpt-4o(36.08)에 근접한 CHrF++ 35.64점의 4B 번역 모델을 llama.cpp용 GGUF로 제공, 로컬 추론에 적합</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
